--- a/Demo/LF/lf-integrated-oncho/demo_lf_itas_9999_3_fts.xlsx
+++ b/Demo/LF/lf-integrated-oncho/demo_lf_itas_9999_3_fts.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
@@ -159,22 +159,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -241,12 +234,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -566,1402 +553,1402 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T56"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
-    <col width="23.5" customWidth="1" style="8" min="1" max="1"/>
-    <col width="19.875" customWidth="1" style="8" min="2" max="2"/>
-    <col width="42.625" customWidth="1" style="16" min="3" max="3"/>
-    <col width="41.25" customWidth="1" style="46" min="4" max="4"/>
-    <col width="12.625" customWidth="1" style="8" min="5" max="5"/>
-    <col width="16.875" customWidth="1" style="8" min="6" max="6"/>
-    <col width="29.5" customWidth="1" style="46" min="7" max="7"/>
-    <col width="49.375" customWidth="1" style="47" min="8" max="8"/>
-    <col width="37.25" customWidth="1" style="8" min="9" max="9"/>
-    <col width="9.75" customWidth="1" style="8" min="10" max="10"/>
-    <col width="35.375" customWidth="1" style="8" min="11" max="11"/>
-    <col width="13.875" customWidth="1" style="8" min="12" max="12"/>
-    <col width="36.625" customWidth="1" style="8" min="13" max="13"/>
-    <col width="11" customWidth="1" style="8" min="14" max="16384"/>
+    <col width="23.5" customWidth="1" style="5" min="1" max="1"/>
+    <col width="19.83203125" customWidth="1" style="5" min="2" max="2"/>
+    <col width="42.58203125" customWidth="1" style="13" min="3" max="3"/>
+    <col width="41.25" customWidth="1" style="41" min="4" max="4"/>
+    <col width="12.58203125" customWidth="1" style="5" min="5" max="5"/>
+    <col width="16.83203125" customWidth="1" style="5" min="6" max="6"/>
+    <col width="29.5" customWidth="1" style="41" min="7" max="7"/>
+    <col width="49.33203125" customWidth="1" style="42" min="8" max="8"/>
+    <col width="37.25" customWidth="1" style="5" min="9" max="9"/>
+    <col width="9.75" customWidth="1" style="5" min="10" max="10"/>
+    <col width="35.33203125" customWidth="1" style="5" min="11" max="11"/>
+    <col width="13.83203125" customWidth="1" style="5" min="12" max="12"/>
+    <col width="36.58203125" customWidth="1" style="5" min="13" max="13"/>
+    <col width="11" customWidth="1" style="5" min="14" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="7">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" customFormat="1" s="4">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" s="21" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>label::English (en)</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>hint::English (en)</t>
         </is>
       </c>
-      <c r="E1" s="21" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>appearance</t>
         </is>
       </c>
-      <c r="F1" s="21" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>constraint</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="19" t="inlineStr">
         <is>
           <t>constraint_message::English (en)</t>
         </is>
       </c>
-      <c r="H1" s="21" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>relevant</t>
         </is>
       </c>
-      <c r="I1" s="21" t="inlineStr">
+      <c r="I1" s="18" t="inlineStr">
         <is>
           <t>calculation</t>
         </is>
       </c>
-      <c r="J1" s="21" t="inlineStr">
+      <c r="J1" s="18" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="K1" s="21" t="inlineStr">
+      <c r="K1" s="18" t="inlineStr">
         <is>
           <t>required_message::English (en)</t>
         </is>
       </c>
-      <c r="L1" s="21" t="inlineStr">
+      <c r="L1" s="18" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="M1" s="21" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>choice_filter</t>
         </is>
       </c>
-      <c r="N1" s="23" t="inlineStr">
+      <c r="N1" s="20" t="inlineStr">
         <is>
           <t>readonly</t>
         </is>
       </c>
-      <c r="O1" s="23" t="inlineStr">
+      <c r="O1" s="20" t="inlineStr">
         <is>
           <t>bind::type</t>
         </is>
       </c>
-      <c r="P1" s="23" t="inlineStr">
+      <c r="P1" s="20" t="inlineStr">
         <is>
           <t>bind::db_get</t>
         </is>
       </c>
-      <c r="Q1" s="23" t="inlineStr">
+      <c r="Q1" s="20" t="inlineStr">
         <is>
           <t>bind::db_filter_by_col_1</t>
         </is>
       </c>
-      <c r="R1" s="23" t="inlineStr">
+      <c r="R1" s="20" t="inlineStr">
         <is>
           <t>bind::db_filter_by_col_2</t>
         </is>
       </c>
-      <c r="S1" s="23" t="inlineStr">
+      <c r="S1" s="20" t="inlineStr">
         <is>
           <t>bind::db_filter_by_col_3</t>
         </is>
       </c>
-      <c r="T1" s="23" t="inlineStr">
+      <c r="T1" s="20" t="inlineStr">
         <is>
           <t>bind::db_filter_by_col_4</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="47.25" customFormat="1" customHeight="1" s="7">
-      <c r="A2" s="31" t="inlineStr">
+    <row r="2" ht="46.5" customFormat="1" customHeight="1" s="4">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>select_one recorder_list</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>recorder</t>
         </is>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>Enter Recorder ID</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>If you are the only recorder on your team, this may be called a "team ID". Recorder ID is the 2-digit code assigned to you or your team.</t>
         </is>
       </c>
-      <c r="E2" s="31" t="n"/>
-      <c r="F2" s="35" t="n"/>
-      <c r="G2" s="25" t="n"/>
-      <c r="H2" s="32" t="n"/>
-      <c r="I2" s="31" t="n"/>
-      <c r="J2" s="31" t="inlineStr">
+      <c r="E2" s="21" t="n"/>
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="23" t="n"/>
+      <c r="I2" s="21" t="n"/>
+      <c r="J2" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K2" s="31" t="n"/>
-      <c r="L2" s="31" t="n"/>
-      <c r="M2" s="31" t="n"/>
-      <c r="N2" s="31" t="n"/>
-      <c r="O2" s="31" t="n"/>
-      <c r="P2" s="31" t="n"/>
-      <c r="Q2" s="31" t="n"/>
-      <c r="R2" s="31" t="n"/>
-      <c r="S2" s="31" t="n"/>
-      <c r="T2" s="31" t="n"/>
-    </row>
-    <row r="3" customFormat="1" s="7">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="K2" s="21" t="n"/>
+      <c r="L2" s="21" t="n"/>
+      <c r="M2" s="21" t="n"/>
+      <c r="N2" s="21" t="n"/>
+      <c r="O2" s="21" t="n"/>
+      <c r="P2" s="21" t="n"/>
+      <c r="Q2" s="21" t="n"/>
+      <c r="R2" s="21" t="n"/>
+      <c r="S2" s="21" t="n"/>
+      <c r="T2" s="21" t="n"/>
+    </row>
+    <row r="3" customFormat="1" s="4">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>admin1</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Select your State/Region/Province</t>
         </is>
       </c>
-      <c r="D3" s="27" t="n"/>
-      <c r="E3" s="31" t="n"/>
-      <c r="F3" s="35" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="32" t="n"/>
-      <c r="I3" s="31" t="n"/>
-      <c r="J3" s="31" t="inlineStr">
+      <c r="D3" s="24" t="n"/>
+      <c r="E3" s="21" t="n"/>
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="23" t="n"/>
+      <c r="I3" s="21" t="n"/>
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K3" s="31" t="n"/>
-      <c r="L3" s="31" t="n"/>
-      <c r="M3" s="31" t="n"/>
-      <c r="N3" s="31" t="n"/>
-      <c r="O3" s="31" t="n"/>
-      <c r="P3" s="31" t="inlineStr">
+      <c r="K3" s="21" t="n"/>
+      <c r="L3" s="21" t="n"/>
+      <c r="M3" s="21" t="n"/>
+      <c r="N3" s="21" t="n"/>
+      <c r="O3" s="21" t="n"/>
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t>col_1</t>
         </is>
       </c>
-      <c r="Q3" s="31" t="n"/>
-      <c r="R3" s="31" t="n"/>
-      <c r="S3" s="31" t="n"/>
-      <c r="T3" s="31" t="n"/>
-    </row>
-    <row r="4" customFormat="1" s="7">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="Q3" s="21" t="n"/>
+      <c r="R3" s="21" t="n"/>
+      <c r="S3" s="21" t="n"/>
+      <c r="T3" s="21" t="n"/>
+    </row>
+    <row r="4" customFormat="1" s="4">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>iu</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Select your Implementation Unit (IU)</t>
         </is>
       </c>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="31" t="n"/>
-      <c r="F4" s="35" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="32" t="n"/>
-      <c r="I4" s="31" t="n"/>
-      <c r="J4" s="31" t="inlineStr">
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="21" t="n"/>
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="22" t="n"/>
+      <c r="H4" s="23" t="n"/>
+      <c r="I4" s="21" t="n"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K4" s="31" t="n"/>
-      <c r="L4" s="31" t="n"/>
-      <c r="M4" s="31" t="n"/>
-      <c r="N4" s="31" t="n"/>
-      <c r="O4" s="31" t="n"/>
-      <c r="P4" s="31" t="inlineStr">
+      <c r="K4" s="21" t="n"/>
+      <c r="L4" s="21" t="n"/>
+      <c r="M4" s="21" t="n"/>
+      <c r="N4" s="21" t="n"/>
+      <c r="O4" s="21" t="n"/>
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t>col_2</t>
         </is>
       </c>
-      <c r="Q4" s="31" t="inlineStr">
+      <c r="Q4" s="21" t="inlineStr">
         <is>
           <t>${admin1}</t>
         </is>
       </c>
-      <c r="R4" s="31" t="n"/>
-      <c r="S4" s="31" t="n"/>
-      <c r="T4" s="31" t="n"/>
-    </row>
-    <row r="5" customFormat="1" s="7">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="R4" s="21" t="n"/>
+      <c r="S4" s="21" t="n"/>
+      <c r="T4" s="21" t="n"/>
+    </row>
+    <row r="5" customFormat="1" s="4">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>Select your site</t>
         </is>
       </c>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="31" t="n"/>
-      <c r="F5" s="35" t="n"/>
-      <c r="G5" s="25" t="n"/>
-      <c r="H5" s="32" t="n"/>
-      <c r="I5" s="31" t="n"/>
-      <c r="J5" s="31" t="inlineStr">
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="21" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="23" t="n"/>
+      <c r="I5" s="21" t="n"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K5" s="31" t="n"/>
-      <c r="L5" s="31" t="n"/>
-      <c r="M5" s="31" t="n"/>
-      <c r="N5" s="31" t="n"/>
-      <c r="O5" s="31" t="n"/>
-      <c r="P5" s="31" t="inlineStr">
+      <c r="K5" s="21" t="n"/>
+      <c r="L5" s="21" t="n"/>
+      <c r="M5" s="21" t="n"/>
+      <c r="N5" s="21" t="n"/>
+      <c r="O5" s="21" t="n"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t>col_3</t>
         </is>
       </c>
-      <c r="Q5" s="31" t="n"/>
-      <c r="R5" s="31" t="inlineStr">
+      <c r="Q5" s="21" t="n"/>
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t>${iu}</t>
         </is>
       </c>
-      <c r="S5" s="31" t="n"/>
-      <c r="T5" s="31" t="n"/>
-    </row>
-    <row r="6" customFormat="1" s="7">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="S5" s="21" t="n"/>
+      <c r="T5" s="21" t="n"/>
+    </row>
+    <row r="6" customFormat="1" s="4">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>site_id</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Select your site code</t>
         </is>
       </c>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="31" t="n"/>
-      <c r="F6" s="35" t="n"/>
-      <c r="G6" s="25" t="n"/>
-      <c r="H6" s="32" t="n"/>
-      <c r="I6" s="31" t="n"/>
-      <c r="J6" s="31" t="inlineStr">
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="21" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="23" t="n"/>
+      <c r="I6" s="21" t="n"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K6" s="31" t="n"/>
-      <c r="L6" s="31" t="n"/>
-      <c r="M6" s="31" t="n"/>
-      <c r="N6" s="31" t="n"/>
-      <c r="O6" s="31" t="n"/>
-      <c r="P6" s="31" t="inlineStr">
+      <c r="K6" s="21" t="n"/>
+      <c r="L6" s="21" t="n"/>
+      <c r="M6" s="21" t="n"/>
+      <c r="N6" s="21" t="n"/>
+      <c r="O6" s="21" t="n"/>
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t>col_4</t>
         </is>
       </c>
-      <c r="Q6" s="31" t="n"/>
-      <c r="R6" s="31" t="n"/>
-      <c r="S6" s="31" t="inlineStr">
+      <c r="Q6" s="21" t="n"/>
+      <c r="R6" s="21" t="n"/>
+      <c r="S6" s="21" t="inlineStr">
         <is>
           <t>${site}</t>
         </is>
       </c>
-      <c r="T6" s="31" t="n"/>
-    </row>
-    <row r="7" customFormat="1" s="7">
-      <c r="A7" s="31" t="n"/>
-      <c r="B7" s="32" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="31" t="n"/>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="25" t="n"/>
-      <c r="H7" s="32" t="n"/>
-      <c r="I7" s="31" t="n"/>
-      <c r="J7" s="31" t="n"/>
-      <c r="K7" s="31" t="n"/>
-      <c r="L7" s="31" t="n"/>
-      <c r="M7" s="31" t="n"/>
-      <c r="N7" s="31" t="n"/>
-      <c r="O7" s="31" t="n"/>
-      <c r="P7" s="31" t="n"/>
-      <c r="Q7" s="31" t="n"/>
-      <c r="R7" s="31" t="n"/>
-      <c r="S7" s="31" t="n"/>
-      <c r="T7" s="31" t="n"/>
-    </row>
-    <row r="8" ht="63" customFormat="1" customHeight="1" s="7">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="T6" s="21" t="n"/>
+    </row>
+    <row r="7" customFormat="1" s="4">
+      <c r="A7" s="21" t="n"/>
+      <c r="B7" s="23" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="21" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="21" t="n"/>
+      <c r="L7" s="21" t="n"/>
+      <c r="M7" s="21" t="n"/>
+      <c r="N7" s="21" t="n"/>
+      <c r="O7" s="21" t="n"/>
+      <c r="P7" s="21" t="n"/>
+      <c r="Q7" s="21" t="n"/>
+      <c r="R7" s="21" t="n"/>
+      <c r="S7" s="21" t="n"/>
+      <c r="T7" s="21" t="n"/>
+    </row>
+    <row r="8" ht="62" customFormat="1" customHeight="1" s="4">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>select_one id_type</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>itype</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Participant ID Code method : Will you scann the barcode/Qrcode or use the code from the participant form (auto-generated or manually entered)?</t>
         </is>
       </c>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="31" t="n"/>
-      <c r="F8" s="35" t="n"/>
-      <c r="G8" s="25" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="31" t="n"/>
-      <c r="J8" s="31" t="inlineStr">
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="21" t="n"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K8" s="31" t="n"/>
-      <c r="L8" s="31" t="n"/>
-      <c r="M8" s="31" t="n"/>
-      <c r="N8" s="31" t="n"/>
-      <c r="O8" s="31" t="n"/>
-      <c r="P8" s="31" t="n"/>
-      <c r="Q8" s="31" t="n"/>
-      <c r="R8" s="31" t="n"/>
-      <c r="S8" s="31" t="n"/>
-      <c r="T8" s="31" t="n"/>
-    </row>
-    <row r="9" ht="94.5" customFormat="1" customHeight="1" s="7">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="K8" s="21" t="n"/>
+      <c r="L8" s="21" t="n"/>
+      <c r="M8" s="21" t="n"/>
+      <c r="N8" s="21" t="n"/>
+      <c r="O8" s="21" t="n"/>
+      <c r="P8" s="21" t="n"/>
+      <c r="Q8" s="21" t="n"/>
+      <c r="R8" s="21" t="n"/>
+      <c r="S8" s="21" t="n"/>
+      <c r="T8" s="21" t="n"/>
+    </row>
+    <row r="9" ht="93" customFormat="1" customHeight="1" s="4">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>select_one warning_note</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>warning_note</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>Important Note for Recorders: To avoid duplicate codes, Use the "Save as draft" option if you haven’t finished registering all results of this Community/Village (survey site). If you need to resume, reopen your draft from the "Saved Forms" list to continue.</t>
         </is>
       </c>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="31" t="n"/>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="25" t="n"/>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="31" t="n"/>
-      <c r="J9" s="31" t="inlineStr">
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="21" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="21" t="n"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K9" s="31" t="n"/>
-      <c r="L9" s="31" t="n"/>
-      <c r="M9" s="31" t="n"/>
-      <c r="N9" s="31" t="n"/>
-      <c r="O9" s="31" t="n"/>
-      <c r="P9" s="31" t="n"/>
-      <c r="Q9" s="31" t="n"/>
-      <c r="R9" s="31" t="n"/>
-      <c r="S9" s="31" t="n"/>
-      <c r="T9" s="31" t="n"/>
-    </row>
-    <row r="10" customFormat="1" s="7">
-      <c r="A10" s="31" t="n"/>
-      <c r="B10" s="32" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="31" t="n"/>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="25" t="n"/>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="31" t="n"/>
-      <c r="J10" s="31" t="n"/>
-      <c r="K10" s="31" t="n"/>
-      <c r="L10" s="31" t="n"/>
-      <c r="M10" s="31" t="n"/>
-      <c r="N10" s="31" t="n"/>
-      <c r="O10" s="31" t="n"/>
-      <c r="P10" s="31" t="n"/>
-      <c r="Q10" s="31" t="n"/>
-      <c r="R10" s="31" t="n"/>
-      <c r="S10" s="31" t="n"/>
-      <c r="T10" s="31" t="n"/>
-    </row>
-    <row r="11" customFormat="1" s="7">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="K9" s="21" t="n"/>
+      <c r="L9" s="21" t="n"/>
+      <c r="M9" s="21" t="n"/>
+      <c r="N9" s="21" t="n"/>
+      <c r="O9" s="21" t="n"/>
+      <c r="P9" s="21" t="n"/>
+      <c r="Q9" s="21" t="n"/>
+      <c r="R9" s="21" t="n"/>
+      <c r="S9" s="21" t="n"/>
+      <c r="T9" s="21" t="n"/>
+    </row>
+    <row r="10" customFormat="1" s="4">
+      <c r="A10" s="21" t="n"/>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="21" t="n"/>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="21" t="n"/>
+      <c r="L10" s="21" t="n"/>
+      <c r="M10" s="21" t="n"/>
+      <c r="N10" s="21" t="n"/>
+      <c r="O10" s="21" t="n"/>
+      <c r="P10" s="21" t="n"/>
+      <c r="Q10" s="21" t="n"/>
+      <c r="R10" s="21" t="n"/>
+      <c r="S10" s="21" t="n"/>
+      <c r="T10" s="21" t="n"/>
+    </row>
+    <row r="11" customFormat="1" s="4">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>c1</t>
         </is>
       </c>
-      <c r="C11" s="37" t="n"/>
-      <c r="D11" s="37" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="38" t="n"/>
-      <c r="G11" s="28" t="n"/>
-      <c r="H11" s="37" t="n"/>
-      <c r="I11" s="36" t="inlineStr">
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="33" t="n"/>
+      <c r="G11" s="25" t="n"/>
+      <c r="H11" s="32" t="n"/>
+      <c r="I11" s="31" t="inlineStr">
         <is>
           <t>join(' ', ${code_id})</t>
         </is>
       </c>
-      <c r="J11" s="36" t="n"/>
-      <c r="K11" s="36" t="n"/>
-      <c r="L11" s="36" t="n"/>
-      <c r="M11" s="36" t="n"/>
-      <c r="N11" s="36" t="n"/>
-      <c r="O11" s="36" t="inlineStr">
+      <c r="J11" s="31" t="n"/>
+      <c r="K11" s="31" t="n"/>
+      <c r="L11" s="31" t="n"/>
+      <c r="M11" s="31" t="n"/>
+      <c r="N11" s="31" t="n"/>
+      <c r="O11" s="31" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="P11" s="36" t="n"/>
-      <c r="Q11" s="36" t="n"/>
-      <c r="R11" s="36" t="n"/>
-      <c r="S11" s="36" t="n"/>
-      <c r="T11" s="36" t="n"/>
-    </row>
-    <row r="12" customFormat="1" s="7">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="P11" s="31" t="n"/>
+      <c r="Q11" s="31" t="n"/>
+      <c r="R11" s="31" t="n"/>
+      <c r="S11" s="31" t="n"/>
+      <c r="T11" s="31" t="n"/>
+    </row>
+    <row r="12" customFormat="1" s="4">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>begin repeat</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>d9999</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Results FTS</t>
         </is>
       </c>
-      <c r="D12" s="29" t="n"/>
-      <c r="E12" s="39" t="n"/>
-      <c r="F12" s="40" t="n"/>
-      <c r="G12" s="30" t="n"/>
-      <c r="H12" s="29" t="n"/>
-      <c r="I12" s="39" t="n"/>
-      <c r="J12" s="39" t="n"/>
-      <c r="K12" s="39" t="n"/>
-      <c r="L12" s="39" t="n"/>
-      <c r="M12" s="39" t="n"/>
-      <c r="N12" s="39" t="n"/>
-      <c r="O12" s="39" t="n"/>
-      <c r="P12" s="39" t="n"/>
-      <c r="Q12" s="39" t="n"/>
-      <c r="R12" s="39" t="n"/>
-      <c r="S12" s="39" t="n"/>
-      <c r="T12" s="39" t="n"/>
-    </row>
-    <row r="13" customFormat="1" s="7">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="34" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="27" t="n"/>
+      <c r="H12" s="26" t="n"/>
+      <c r="I12" s="34" t="n"/>
+      <c r="J12" s="34" t="n"/>
+      <c r="K12" s="34" t="n"/>
+      <c r="L12" s="34" t="n"/>
+      <c r="M12" s="34" t="n"/>
+      <c r="N12" s="34" t="n"/>
+      <c r="O12" s="34" t="n"/>
+      <c r="P12" s="34" t="n"/>
+      <c r="Q12" s="34" t="n"/>
+      <c r="R12" s="34" t="n"/>
+      <c r="S12" s="34" t="n"/>
+      <c r="T12" s="34" t="n"/>
+    </row>
+    <row r="13" customFormat="1" s="4">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>c2</t>
         </is>
       </c>
-      <c r="C13" s="37" t="n"/>
-      <c r="D13" s="37" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="38" t="n"/>
-      <c r="G13" s="28" t="n"/>
-      <c r="H13" s="37" t="n"/>
-      <c r="I13" s="36" t="inlineStr">
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="33" t="n"/>
+      <c r="G13" s="25" t="n"/>
+      <c r="H13" s="32" t="n"/>
+      <c r="I13" s="31" t="inlineStr">
         <is>
           <t>position(..)</t>
         </is>
       </c>
-      <c r="J13" s="36" t="n"/>
-      <c r="K13" s="36" t="n"/>
-      <c r="L13" s="36" t="n"/>
-      <c r="M13" s="36" t="n"/>
-      <c r="N13" s="36" t="n"/>
-      <c r="O13" s="36" t="inlineStr">
+      <c r="J13" s="31" t="n"/>
+      <c r="K13" s="31" t="n"/>
+      <c r="L13" s="31" t="n"/>
+      <c r="M13" s="31" t="n"/>
+      <c r="N13" s="31" t="n"/>
+      <c r="O13" s="31" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="P13" s="36" t="n"/>
-      <c r="Q13" s="36" t="n"/>
-      <c r="R13" s="36" t="n"/>
-      <c r="S13" s="36" t="n"/>
-      <c r="T13" s="36" t="n"/>
-    </row>
-    <row r="14" customFormat="1" s="7">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="P13" s="31" t="n"/>
+      <c r="Q13" s="31" t="n"/>
+      <c r="R13" s="31" t="n"/>
+      <c r="S13" s="31" t="n"/>
+      <c r="T13" s="31" t="n"/>
+    </row>
+    <row r="14" customFormat="1" s="4">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>c3</t>
         </is>
       </c>
-      <c r="C14" s="37" t="n"/>
-      <c r="D14" s="37" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="38" t="n"/>
-      <c r="G14" s="28" t="n"/>
-      <c r="H14" s="37" t="n"/>
-      <c r="I14" s="36" t="inlineStr">
+      <c r="C14" s="32" t="n"/>
+      <c r="D14" s="32" t="n"/>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="33" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="32" t="n"/>
+      <c r="I14" s="31" t="inlineStr">
         <is>
           <t>if (${c2} = 1,'',substring-after(${c1},${code_id}))</t>
         </is>
       </c>
-      <c r="J14" s="36" t="n"/>
-      <c r="K14" s="36" t="n"/>
-      <c r="L14" s="36" t="n"/>
-      <c r="M14" s="36" t="n"/>
-      <c r="N14" s="36" t="n"/>
-      <c r="O14" s="36" t="inlineStr">
+      <c r="J14" s="31" t="n"/>
+      <c r="K14" s="31" t="n"/>
+      <c r="L14" s="31" t="n"/>
+      <c r="M14" s="31" t="n"/>
+      <c r="N14" s="31" t="n"/>
+      <c r="O14" s="31" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="P14" s="36" t="n"/>
-      <c r="Q14" s="36" t="n"/>
-      <c r="R14" s="36" t="n"/>
-      <c r="S14" s="36" t="n"/>
-      <c r="T14" s="36" t="n"/>
-    </row>
-    <row r="15" customFormat="1" s="7">
-      <c r="A15" s="31" t="n"/>
-      <c r="B15" s="32" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="31" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="25" t="n"/>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="31" t="n"/>
-      <c r="J15" s="31" t="n"/>
-      <c r="K15" s="31" t="n"/>
-      <c r="L15" s="31" t="n"/>
-      <c r="M15" s="31" t="n"/>
-      <c r="N15" s="31" t="n"/>
-      <c r="O15" s="31" t="n"/>
-      <c r="P15" s="31" t="n"/>
-      <c r="Q15" s="31" t="n"/>
-      <c r="R15" s="31" t="n"/>
-      <c r="S15" s="31" t="n"/>
-      <c r="T15" s="31" t="n"/>
-    </row>
-    <row r="16" ht="31.5" customFormat="1" customHeight="1" s="7">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="P14" s="31" t="n"/>
+      <c r="Q14" s="31" t="n"/>
+      <c r="R14" s="31" t="n"/>
+      <c r="S14" s="31" t="n"/>
+      <c r="T14" s="31" t="n"/>
+    </row>
+    <row r="15" customFormat="1" s="4">
+      <c r="A15" s="21" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="23" t="n"/>
+      <c r="I15" s="21" t="n"/>
+      <c r="J15" s="21" t="n"/>
+      <c r="K15" s="21" t="n"/>
+      <c r="L15" s="21" t="n"/>
+      <c r="M15" s="21" t="n"/>
+      <c r="N15" s="21" t="n"/>
+      <c r="O15" s="21" t="n"/>
+      <c r="P15" s="21" t="n"/>
+      <c r="Q15" s="21" t="n"/>
+      <c r="R15" s="21" t="n"/>
+      <c r="S15" s="21" t="n"/>
+      <c r="T15" s="21" t="n"/>
+    </row>
+    <row r="16" ht="31" customFormat="1" customHeight="1" s="4">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>code_id1</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Select the unique participant code as generated in the form 2 (participant)</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>${itype} = 'ID_generation'</t>
         </is>
       </c>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="15" t="n"/>
-      <c r="K16" s="14" t="n"/>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14" t="n"/>
-      <c r="N16" s="14" t="n"/>
-      <c r="O16" s="31" t="n"/>
-      <c r="P16" s="41" t="inlineStr">
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="11" t="n"/>
+      <c r="L16" s="11" t="n"/>
+      <c r="M16" s="11" t="n"/>
+      <c r="N16" s="11" t="n"/>
+      <c r="O16" s="21" t="n"/>
+      <c r="P16" s="36" t="inlineStr">
         <is>
           <t>col_5</t>
         </is>
       </c>
-      <c r="Q16" s="31" t="n"/>
-      <c r="R16" s="31" t="n"/>
-      <c r="S16" s="31" t="n"/>
-      <c r="T16" s="41" t="inlineStr">
+      <c r="Q16" s="21" t="n"/>
+      <c r="R16" s="21" t="n"/>
+      <c r="S16" s="21" t="n"/>
+      <c r="T16" s="36" t="inlineStr">
         <is>
           <t>${site_id}</t>
         </is>
       </c>
     </row>
-    <row r="17" customFormat="1" s="7">
-      <c r="A17" s="31" t="n"/>
-      <c r="B17" s="32" t="n"/>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17" s="27" t="n"/>
-      <c r="E17" s="31" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="25" t="n"/>
-      <c r="H17" s="32" t="n"/>
-      <c r="I17" s="31" t="n"/>
-      <c r="J17" s="31" t="n"/>
-      <c r="K17" s="31" t="n"/>
-      <c r="L17" s="31" t="n"/>
-      <c r="M17" s="31" t="n"/>
-      <c r="N17" s="31" t="n"/>
-      <c r="O17" s="31" t="n"/>
-      <c r="P17" s="31" t="n"/>
-      <c r="Q17" s="31" t="n"/>
-      <c r="R17" s="31" t="n"/>
-      <c r="S17" s="31" t="n"/>
-      <c r="T17" s="31" t="n"/>
-    </row>
-    <row r="18" customFormat="1" s="7">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="17" customFormat="1" s="4">
+      <c r="A17" s="21" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="23" t="n"/>
+      <c r="I17" s="21" t="n"/>
+      <c r="J17" s="21" t="n"/>
+      <c r="K17" s="21" t="n"/>
+      <c r="L17" s="21" t="n"/>
+      <c r="M17" s="21" t="n"/>
+      <c r="N17" s="21" t="n"/>
+      <c r="O17" s="21" t="n"/>
+      <c r="P17" s="21" t="n"/>
+      <c r="Q17" s="21" t="n"/>
+      <c r="R17" s="21" t="n"/>
+      <c r="S17" s="21" t="n"/>
+      <c r="T17" s="21" t="n"/>
+    </row>
+    <row r="18" customFormat="1" s="4">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>select_one barcode_method</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>barcode_method</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>QR code / Barcode method:</t>
         </is>
       </c>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>${itype} = 'Scanner'</t>
         </is>
       </c>
-      <c r="I18" s="11" t="n"/>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K18" s="11" t="n"/>
-      <c r="L18" s="11" t="n"/>
-      <c r="M18" s="11" t="n"/>
-      <c r="N18" s="11" t="n"/>
-      <c r="O18" s="31" t="n"/>
-      <c r="P18" s="31" t="n"/>
-      <c r="Q18" s="31" t="n"/>
-      <c r="R18" s="31" t="n"/>
-      <c r="S18" s="31" t="n"/>
-      <c r="T18" s="31" t="n"/>
-    </row>
-    <row r="19" ht="31.5" customFormat="1" customHeight="1" s="7">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="8" t="n"/>
+      <c r="N18" s="8" t="n"/>
+      <c r="O18" s="21" t="n"/>
+      <c r="P18" s="21" t="n"/>
+      <c r="Q18" s="21" t="n"/>
+      <c r="R18" s="21" t="n"/>
+      <c r="S18" s="21" t="n"/>
+      <c r="T18" s="21" t="n"/>
+    </row>
+    <row r="19" ht="31" customFormat="1" customHeight="1" s="4">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>barcode</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>code_id3</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Please scan the QR code / Barcode of the participant</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="42" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>${barcode_method} = 'QRScann'</t>
         </is>
       </c>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K19" s="11" t="n"/>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="31" t="n"/>
-      <c r="P19" s="31" t="n"/>
-      <c r="Q19" s="31" t="n"/>
-      <c r="R19" s="31" t="n"/>
-      <c r="S19" s="31" t="n"/>
-      <c r="T19" s="31" t="n"/>
-    </row>
-    <row r="20" ht="31.5" customFormat="1" customHeight="1" s="7">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="21" t="n"/>
+      <c r="P19" s="21" t="n"/>
+      <c r="Q19" s="21" t="n"/>
+      <c r="R19" s="21" t="n"/>
+      <c r="S19" s="21" t="n"/>
+      <c r="T19" s="21" t="n"/>
+    </row>
+    <row r="20" ht="31" customFormat="1" customHeight="1" s="4">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>code_id4</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Please enter the QR code / Barcode of this participant</t>
         </is>
       </c>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="42" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>${barcode_method} = 'QRManual'</t>
         </is>
       </c>
-      <c r="I20" s="11" t="n"/>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K20" s="11" t="n"/>
-      <c r="L20" s="11" t="n"/>
-      <c r="M20" s="11" t="n"/>
-      <c r="N20" s="11" t="n"/>
-      <c r="O20" s="31" t="n"/>
-      <c r="P20" s="31" t="n"/>
-      <c r="Q20" s="31" t="n"/>
-      <c r="R20" s="31" t="n"/>
-      <c r="S20" s="31" t="n"/>
-      <c r="T20" s="31" t="n"/>
-    </row>
-    <row r="21" ht="31.5" customFormat="1" customHeight="1" s="7">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="21" t="n"/>
+      <c r="P20" s="21" t="n"/>
+      <c r="Q20" s="21" t="n"/>
+      <c r="R20" s="21" t="n"/>
+      <c r="S20" s="21" t="n"/>
+      <c r="T20" s="21" t="n"/>
+    </row>
+    <row r="21" ht="31" customFormat="1" customHeight="1" s="4">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>code_id5</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Please re-enter the QR code / Barcode</t>
         </is>
       </c>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="42" t="inlineStr">
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>. = ${code_id4}</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>The repeated code must be the same as previouly entered</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>${barcode_method} = 'QRManual'</t>
         </is>
       </c>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K21" s="11" t="n"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="11" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="31" t="n"/>
-      <c r="P21" s="31" t="n"/>
-      <c r="Q21" s="31" t="n"/>
-      <c r="R21" s="31" t="n"/>
-      <c r="S21" s="31" t="n"/>
-      <c r="T21" s="31" t="n"/>
-    </row>
-    <row r="22" customFormat="1" s="7">
-      <c r="A22" s="31" t="n"/>
-      <c r="B22" s="32" t="n"/>
-      <c r="C22" s="27" t="n"/>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="31" t="n"/>
-      <c r="F22" s="35" t="n"/>
-      <c r="G22" s="25" t="n"/>
-      <c r="H22" s="32" t="n"/>
-      <c r="I22" s="31" t="n"/>
-      <c r="J22" s="31" t="n"/>
-      <c r="K22" s="31" t="n"/>
-      <c r="L22" s="31" t="n"/>
-      <c r="M22" s="31" t="n"/>
-      <c r="N22" s="31" t="n"/>
-      <c r="O22" s="31" t="n"/>
-      <c r="P22" s="31" t="n"/>
-      <c r="Q22" s="31" t="n"/>
-      <c r="R22" s="31" t="n"/>
-      <c r="S22" s="31" t="n"/>
-      <c r="T22" s="31" t="n"/>
-    </row>
-    <row r="23" customFormat="1" s="7">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="K21" s="8" t="n"/>
+      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
+      <c r="N21" s="8" t="n"/>
+      <c r="O21" s="21" t="n"/>
+      <c r="P21" s="21" t="n"/>
+      <c r="Q21" s="21" t="n"/>
+      <c r="R21" s="21" t="n"/>
+      <c r="S21" s="21" t="n"/>
+      <c r="T21" s="21" t="n"/>
+    </row>
+    <row r="22" customFormat="1" s="4">
+      <c r="A22" s="21" t="n"/>
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="23" t="n"/>
+      <c r="I22" s="21" t="n"/>
+      <c r="J22" s="21" t="n"/>
+      <c r="K22" s="21" t="n"/>
+      <c r="L22" s="21" t="n"/>
+      <c r="M22" s="21" t="n"/>
+      <c r="N22" s="21" t="n"/>
+      <c r="O22" s="21" t="n"/>
+      <c r="P22" s="21" t="n"/>
+      <c r="Q22" s="21" t="n"/>
+      <c r="R22" s="21" t="n"/>
+      <c r="S22" s="21" t="n"/>
+      <c r="T22" s="21" t="n"/>
+    </row>
+    <row r="23" customFormat="1" s="4">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>code_id</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>The unique participant ID Code is :</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>not(selected(${c3}, .))</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Error! This code has already been used</t>
         </is>
       </c>
-      <c r="H23" s="10" t="n"/>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>if(${itype} = 'ID_generation', ${code_id1}, if(${barcode_method} = 'QRScann', ${code_id3}, ${code_id5}))</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K23" s="9" t="n"/>
-      <c r="L23" s="9" t="n"/>
-      <c r="M23" s="9" t="n"/>
-      <c r="N23" s="9" t="inlineStr">
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O23" s="31" t="n"/>
-      <c r="P23" s="31" t="n"/>
-      <c r="Q23" s="31" t="n"/>
-      <c r="R23" s="31" t="n"/>
-      <c r="S23" s="31" t="n"/>
-      <c r="T23" s="31" t="n"/>
-    </row>
-    <row r="24" customFormat="1" s="7">
-      <c r="A24" s="31" t="n"/>
-      <c r="B24" s="32" t="n"/>
-      <c r="C24" s="32" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="31" t="n"/>
-      <c r="H24" s="32" t="n"/>
-      <c r="I24" s="31" t="n"/>
-      <c r="J24" s="32" t="n"/>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n"/>
-      <c r="N24" s="31" t="n"/>
-      <c r="O24" s="31" t="n"/>
-      <c r="P24" s="41" t="n"/>
-      <c r="Q24" s="31" t="n"/>
-      <c r="R24" s="31" t="n"/>
-      <c r="S24" s="31" t="n"/>
-      <c r="T24" s="41" t="n"/>
-    </row>
-    <row r="25" ht="31.5" customFormat="1" customHeight="1" s="7">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="O23" s="21" t="n"/>
+      <c r="P23" s="21" t="n"/>
+      <c r="Q23" s="21" t="n"/>
+      <c r="R23" s="21" t="n"/>
+      <c r="S23" s="21" t="n"/>
+      <c r="T23" s="21" t="n"/>
+    </row>
+    <row r="24" customFormat="1" s="4">
+      <c r="A24" s="21" t="n"/>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="23" t="n"/>
+      <c r="I24" s="21" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="21" t="n"/>
+      <c r="L24" s="21" t="n"/>
+      <c r="M24" s="21" t="n"/>
+      <c r="N24" s="21" t="n"/>
+      <c r="O24" s="21" t="n"/>
+      <c r="P24" s="36" t="n"/>
+      <c r="Q24" s="21" t="n"/>
+      <c r="R24" s="21" t="n"/>
+      <c r="S24" s="21" t="n"/>
+      <c r="T24" s="36" t="n"/>
+    </row>
+    <row r="25" ht="31" customFormat="1" customHeight="1" s="4">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B25" s="32" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>lotnumber1</t>
         </is>
       </c>
-      <c r="C25" s="27" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>Please enter FTS lot number 1</t>
         </is>
       </c>
-      <c r="D25" s="27" t="n"/>
-      <c r="E25" s="31" t="n"/>
-      <c r="F25" s="32" t="inlineStr">
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>regex(.,'^[0-9]{6}$')</t>
         </is>
       </c>
-      <c r="G25" s="27" t="inlineStr">
+      <c r="G25" s="24" t="inlineStr">
         <is>
           <t>This number must be a six-digit number</t>
         </is>
       </c>
-      <c r="H25" s="32" t="n"/>
-      <c r="I25" s="32" t="n"/>
-      <c r="J25" s="31" t="inlineStr">
+      <c r="H25" s="23" t="n"/>
+      <c r="I25" s="23" t="n"/>
+      <c r="J25" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K25" s="31" t="n"/>
-      <c r="L25" s="31" t="n"/>
-      <c r="M25" s="31" t="n"/>
-      <c r="N25" s="31" t="n"/>
-      <c r="O25" s="31" t="n"/>
-      <c r="P25" s="31" t="n"/>
-      <c r="Q25" s="31" t="n"/>
-      <c r="R25" s="31" t="n"/>
-      <c r="S25" s="31" t="n"/>
-      <c r="T25" s="31" t="n"/>
-    </row>
-    <row r="26" customFormat="1" s="7">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="K25" s="21" t="n"/>
+      <c r="L25" s="21" t="n"/>
+      <c r="M25" s="21" t="n"/>
+      <c r="N25" s="21" t="n"/>
+      <c r="O25" s="21" t="n"/>
+      <c r="P25" s="21" t="n"/>
+      <c r="Q25" s="21" t="n"/>
+      <c r="R25" s="21" t="n"/>
+      <c r="S25" s="21" t="n"/>
+      <c r="T25" s="21" t="n"/>
+    </row>
+    <row r="26" customFormat="1" s="4">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>select_one results_list</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>fts_result1</t>
         </is>
       </c>
-      <c r="C26" s="27" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>FTS -  Test 1</t>
         </is>
       </c>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="n"/>
-      <c r="G26" s="43" t="n"/>
-      <c r="H26" s="32" t="n"/>
-      <c r="I26" s="32" t="n"/>
-      <c r="J26" s="31" t="inlineStr">
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="38" t="n"/>
+      <c r="H26" s="23" t="n"/>
+      <c r="I26" s="23" t="n"/>
+      <c r="J26" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K26" s="31" t="n"/>
-      <c r="L26" s="31" t="n"/>
-      <c r="M26" s="31" t="n"/>
-      <c r="N26" s="31" t="n"/>
-      <c r="O26" s="31" t="n"/>
-      <c r="P26" s="31" t="n"/>
-      <c r="Q26" s="31" t="n"/>
-      <c r="R26" s="31" t="n"/>
-      <c r="S26" s="31" t="n"/>
-      <c r="T26" s="31" t="n"/>
-    </row>
-    <row r="27" customFormat="1" s="7">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="K26" s="21" t="n"/>
+      <c r="L26" s="21" t="n"/>
+      <c r="M26" s="21" t="n"/>
+      <c r="N26" s="21" t="n"/>
+      <c r="O26" s="21" t="n"/>
+      <c r="P26" s="21" t="n"/>
+      <c r="Q26" s="21" t="n"/>
+      <c r="R26" s="21" t="n"/>
+      <c r="S26" s="21" t="n"/>
+      <c r="T26" s="21" t="n"/>
+    </row>
+    <row r="27" customFormat="1" s="4">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>select_multiple why_invalid</t>
         </is>
       </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>why_invalid1</t>
         </is>
       </c>
-      <c r="C27" s="27" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>Give reason for invalid test</t>
         </is>
       </c>
-      <c r="D27" s="27" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="31" t="n"/>
-      <c r="G27" s="43" t="n"/>
-      <c r="H27" s="32" t="inlineStr">
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="21" t="n"/>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="38" t="n"/>
+      <c r="H27" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">${fts_result1} = 'Invalid' </t>
         </is>
       </c>
-      <c r="I27" s="32" t="n"/>
-      <c r="J27" s="31" t="inlineStr">
+      <c r="I27" s="23" t="n"/>
+      <c r="J27" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K27" s="31" t="n"/>
-      <c r="L27" s="31" t="n"/>
-      <c r="M27" s="31" t="n"/>
-      <c r="N27" s="31" t="n"/>
-      <c r="O27" s="31" t="n"/>
-      <c r="P27" s="31" t="n"/>
-      <c r="Q27" s="31" t="n"/>
-      <c r="R27" s="31" t="n"/>
-      <c r="S27" s="31" t="n"/>
-      <c r="T27" s="31" t="n"/>
-    </row>
-    <row r="28" customFormat="1" s="7">
-      <c r="A28" s="31" t="inlineStr">
+      <c r="K27" s="21" t="n"/>
+      <c r="L27" s="21" t="n"/>
+      <c r="M27" s="21" t="n"/>
+      <c r="N27" s="21" t="n"/>
+      <c r="O27" s="21" t="n"/>
+      <c r="P27" s="21" t="n"/>
+      <c r="Q27" s="21" t="n"/>
+      <c r="R27" s="21" t="n"/>
+      <c r="S27" s="21" t="n"/>
+      <c r="T27" s="21" t="n"/>
+    </row>
+    <row r="28" customFormat="1" s="4">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>why_invalid_other1</t>
         </is>
       </c>
-      <c r="C28" s="27" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>Give reason for invalid test</t>
         </is>
       </c>
-      <c r="D28" s="27" t="n"/>
-      <c r="E28" s="31" t="n"/>
-      <c r="F28" s="31" t="n"/>
-      <c r="G28" s="43" t="n"/>
-      <c r="H28" s="32" t="inlineStr">
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="21" t="n"/>
+      <c r="F28" s="21" t="n"/>
+      <c r="G28" s="38" t="n"/>
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>selected(${why_invalid1},'Other')</t>
         </is>
       </c>
-      <c r="I28" s="32" t="n"/>
-      <c r="J28" s="31" t="inlineStr">
+      <c r="I28" s="23" t="n"/>
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K28" s="31" t="n"/>
-      <c r="L28" s="31" t="n"/>
-      <c r="M28" s="31" t="n"/>
-      <c r="N28" s="31" t="n"/>
-      <c r="O28" s="31" t="n"/>
-      <c r="P28" s="31" t="n"/>
-      <c r="Q28" s="31" t="n"/>
-      <c r="R28" s="31" t="n"/>
-      <c r="S28" s="31" t="n"/>
-      <c r="T28" s="31" t="n"/>
-    </row>
-    <row r="29" customFormat="1" s="7">
-      <c r="A29" s="31" t="n"/>
-      <c r="B29" s="32" t="n"/>
-      <c r="C29" s="27" t="n"/>
-      <c r="D29" s="27" t="n"/>
-      <c r="E29" s="31" t="n"/>
-      <c r="F29" s="31" t="n"/>
-      <c r="G29" s="43" t="n"/>
-      <c r="H29" s="32" t="n"/>
-      <c r="I29" s="31" t="n"/>
-      <c r="J29" s="31" t="n"/>
-      <c r="K29" s="31" t="n"/>
-      <c r="L29" s="31" t="n"/>
-      <c r="M29" s="31" t="n"/>
-      <c r="N29" s="31" t="n"/>
-      <c r="O29" s="31" t="n"/>
-      <c r="P29" s="31" t="n"/>
-      <c r="Q29" s="31" t="n"/>
-      <c r="R29" s="31" t="n"/>
-      <c r="S29" s="31" t="n"/>
-      <c r="T29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="63" customFormat="1" customHeight="1" s="7">
-      <c r="A30" s="31" t="inlineStr">
+      <c r="K28" s="21" t="n"/>
+      <c r="L28" s="21" t="n"/>
+      <c r="M28" s="21" t="n"/>
+      <c r="N28" s="21" t="n"/>
+      <c r="O28" s="21" t="n"/>
+      <c r="P28" s="21" t="n"/>
+      <c r="Q28" s="21" t="n"/>
+      <c r="R28" s="21" t="n"/>
+      <c r="S28" s="21" t="n"/>
+      <c r="T28" s="21" t="n"/>
+    </row>
+    <row r="29" customFormat="1" s="4">
+      <c r="A29" s="21" t="n"/>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="21" t="n"/>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="38" t="n"/>
+      <c r="H29" s="23" t="n"/>
+      <c r="I29" s="21" t="n"/>
+      <c r="J29" s="21" t="n"/>
+      <c r="K29" s="21" t="n"/>
+      <c r="L29" s="21" t="n"/>
+      <c r="M29" s="21" t="n"/>
+      <c r="N29" s="21" t="n"/>
+      <c r="O29" s="21" t="n"/>
+      <c r="P29" s="21" t="n"/>
+      <c r="Q29" s="21" t="n"/>
+      <c r="R29" s="21" t="n"/>
+      <c r="S29" s="21" t="n"/>
+      <c r="T29" s="21" t="n"/>
+    </row>
+    <row r="30" ht="62" customFormat="1" customHeight="1" s="4">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B30" s="33" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>second_fts_note</t>
         </is>
       </c>
-      <c r="C30" s="34" t="inlineStr">
+      <c r="C30" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">This participant's first FTS test result was ${fts_result1}.  This result requires a second test.  Continue this questionnaire to enter the participant's second test result.  </t>
         </is>
       </c>
-      <c r="D30" s="44" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="31" t="n"/>
-      <c r="G30" s="43" t="n"/>
-      <c r="H30" s="32" t="inlineStr">
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="21" t="n"/>
+      <c r="F30" s="21" t="n"/>
+      <c r="G30" s="38" t="n"/>
+      <c r="H30" s="23" t="inlineStr">
         <is>
           <t>${fts_result1} = 'Invalid'</t>
         </is>
       </c>
-      <c r="I30" s="31" t="n"/>
-      <c r="J30" s="31" t="n"/>
-      <c r="K30" s="31" t="n"/>
-      <c r="L30" s="31" t="n"/>
-      <c r="M30" s="31" t="n"/>
-      <c r="N30" s="31" t="n"/>
-      <c r="O30" s="31" t="n"/>
-      <c r="P30" s="31" t="n"/>
-      <c r="Q30" s="31" t="n"/>
-      <c r="R30" s="31" t="n"/>
-      <c r="S30" s="31" t="n"/>
-      <c r="T30" s="31" t="n"/>
-    </row>
-    <row r="31" ht="31.5" customFormat="1" customHeight="1" s="7">
-      <c r="A31" s="31" t="inlineStr">
+      <c r="I30" s="21" t="n"/>
+      <c r="J30" s="21" t="n"/>
+      <c r="K30" s="21" t="n"/>
+      <c r="L30" s="21" t="n"/>
+      <c r="M30" s="21" t="n"/>
+      <c r="N30" s="21" t="n"/>
+      <c r="O30" s="21" t="n"/>
+      <c r="P30" s="21" t="n"/>
+      <c r="Q30" s="21" t="n"/>
+      <c r="R30" s="21" t="n"/>
+      <c r="S30" s="21" t="n"/>
+      <c r="T30" s="21" t="n"/>
+    </row>
+    <row r="31" ht="31" customFormat="1" customHeight="1" s="4">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>lotnumber2</t>
         </is>
       </c>
-      <c r="C31" s="34" t="inlineStr">
+      <c r="C31" s="29" t="inlineStr">
         <is>
           <t>Please enter FTS lot number 2</t>
         </is>
       </c>
-      <c r="D31" s="44" t="n"/>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="32" t="inlineStr">
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="21" t="n"/>
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>regex(.,'^[0-9]{6}$')</t>
         </is>
       </c>
-      <c r="G31" s="27" t="inlineStr">
+      <c r="G31" s="24" t="inlineStr">
         <is>
           <t>The code must be a six-digit number</t>
         </is>
       </c>
-      <c r="H31" s="32" t="inlineStr">
+      <c r="H31" s="23" t="inlineStr">
         <is>
           <t>${fts_result1} = 'Invalid'</t>
         </is>
       </c>
-      <c r="I31" s="31" t="n"/>
-      <c r="J31" s="31" t="n"/>
-      <c r="K31" s="31" t="n"/>
-      <c r="L31" s="31" t="n"/>
-      <c r="M31" s="31" t="n"/>
-      <c r="N31" s="31" t="n"/>
-      <c r="O31" s="31" t="n"/>
-      <c r="P31" s="31" t="n"/>
-      <c r="Q31" s="31" t="n"/>
-      <c r="R31" s="31" t="n"/>
-      <c r="S31" s="31" t="n"/>
-      <c r="T31" s="31" t="n"/>
+      <c r="I31" s="21" t="n"/>
+      <c r="J31" s="21" t="n"/>
+      <c r="K31" s="21" t="n"/>
+      <c r="L31" s="21" t="n"/>
+      <c r="M31" s="21" t="n"/>
+      <c r="N31" s="21" t="n"/>
+      <c r="O31" s="21" t="n"/>
+      <c r="P31" s="21" t="n"/>
+      <c r="Q31" s="21" t="n"/>
+      <c r="R31" s="21" t="n"/>
+      <c r="S31" s="21" t="n"/>
+      <c r="T31" s="21" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>select_one results_list</t>
         </is>
       </c>
-      <c r="B32" s="33" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>fts_result2</t>
         </is>
       </c>
-      <c r="C32" s="34" t="inlineStr">
+      <c r="C32" s="29" t="inlineStr">
         <is>
           <t>FTS -  Test 2</t>
         </is>
       </c>
-      <c r="D32" s="44" t="n"/>
-      <c r="E32" s="33" t="n"/>
-      <c r="F32" s="33" t="n"/>
-      <c r="G32" s="44" t="n"/>
-      <c r="H32" s="32" t="inlineStr">
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="39" t="n"/>
+      <c r="H32" s="23" t="inlineStr">
         <is>
           <t>${fts_result1} = 'Invalid'</t>
         </is>
       </c>
-      <c r="I32" s="33" t="n"/>
-      <c r="J32" s="31" t="inlineStr">
+      <c r="I32" s="28" t="n"/>
+      <c r="J32" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K32" s="33" t="n"/>
-      <c r="L32" s="33" t="n"/>
-      <c r="M32" s="33" t="n"/>
-      <c r="N32" s="33" t="n"/>
-      <c r="O32" s="33" t="n"/>
-      <c r="P32" s="33" t="n"/>
-      <c r="Q32" s="33" t="n"/>
-      <c r="R32" s="33" t="n"/>
-      <c r="S32" s="33" t="n"/>
-      <c r="T32" s="33" t="n"/>
+      <c r="K32" s="28" t="n"/>
+      <c r="L32" s="28" t="n"/>
+      <c r="M32" s="28" t="n"/>
+      <c r="N32" s="28" t="n"/>
+      <c r="O32" s="28" t="n"/>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n"/>
+      <c r="R32" s="28" t="n"/>
+      <c r="S32" s="28" t="n"/>
+      <c r="T32" s="28" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>select_multiple why_invalid</t>
         </is>
       </c>
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>why_invalid2</t>
         </is>
       </c>
-      <c r="C33" s="34" t="inlineStr">
+      <c r="C33" s="29" t="inlineStr">
         <is>
           <t>Give reason for invalid test 2</t>
         </is>
       </c>
-      <c r="D33" s="44" t="n"/>
-      <c r="E33" s="33" t="n"/>
-      <c r="F33" s="33" t="n"/>
-      <c r="G33" s="44" t="n"/>
-      <c r="H33" s="32" t="inlineStr">
+      <c r="D33" s="39" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="39" t="n"/>
+      <c r="H33" s="23" t="inlineStr">
         <is>
           <t>${fts_result2} = 'Invalid'</t>
         </is>
       </c>
-      <c r="I33" s="33" t="n"/>
-      <c r="J33" s="31" t="inlineStr">
+      <c r="I33" s="28" t="n"/>
+      <c r="J33" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K33" s="33" t="n"/>
-      <c r="L33" s="33" t="n"/>
-      <c r="M33" s="33" t="n"/>
-      <c r="N33" s="33" t="n"/>
-      <c r="O33" s="33" t="n"/>
-      <c r="P33" s="33" t="n"/>
-      <c r="Q33" s="33" t="n"/>
-      <c r="R33" s="33" t="n"/>
-      <c r="S33" s="33" t="n"/>
-      <c r="T33" s="33" t="n"/>
+      <c r="K33" s="28" t="n"/>
+      <c r="L33" s="28" t="n"/>
+      <c r="M33" s="28" t="n"/>
+      <c r="N33" s="28" t="n"/>
+      <c r="O33" s="28" t="n"/>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n"/>
+      <c r="R33" s="28" t="n"/>
+      <c r="S33" s="28" t="n"/>
+      <c r="T33" s="28" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="31" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B34" s="33" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>why_invalid_other2</t>
         </is>
       </c>
-      <c r="C34" s="34" t="inlineStr">
+      <c r="C34" s="29" t="inlineStr">
         <is>
           <t>Give 'Other' reason for invalid test 2</t>
         </is>
       </c>
-      <c r="D34" s="44" t="n"/>
-      <c r="E34" s="33" t="n"/>
-      <c r="F34" s="33" t="n"/>
-      <c r="G34" s="44" t="n"/>
-      <c r="H34" s="32" t="inlineStr">
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="39" t="n"/>
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>selected(${why_invalid2},'Other')</t>
         </is>
       </c>
-      <c r="I34" s="33" t="n"/>
-      <c r="J34" s="31" t="inlineStr">
+      <c r="I34" s="28" t="n"/>
+      <c r="J34" s="21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K34" s="33" t="n"/>
-      <c r="L34" s="33" t="n"/>
-      <c r="M34" s="33" t="n"/>
-      <c r="N34" s="33" t="n"/>
-      <c r="O34" s="33" t="n"/>
-      <c r="P34" s="33" t="n"/>
-      <c r="Q34" s="33" t="n"/>
-      <c r="R34" s="33" t="n"/>
-      <c r="S34" s="33" t="n"/>
-      <c r="T34" s="33" t="n"/>
+      <c r="K34" s="28" t="n"/>
+      <c r="L34" s="28" t="n"/>
+      <c r="M34" s="28" t="n"/>
+      <c r="N34" s="28" t="n"/>
+      <c r="O34" s="28" t="n"/>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n"/>
+      <c r="R34" s="28" t="n"/>
+      <c r="S34" s="28" t="n"/>
+      <c r="T34" s="28" t="n"/>
     </row>
     <row r="35" ht="99.75" customHeight="1">
-      <c r="A35" s="31" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B35" s="33" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>final_result</t>
         </is>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C35" s="29" t="inlineStr">
         <is>
           <t>Final Result</t>
         </is>
       </c>
-      <c r="D35" s="44" t="n"/>
-      <c r="E35" s="33" t="n"/>
-      <c r="F35" s="33" t="n"/>
-      <c r="G35" s="44" t="n"/>
-      <c r="H35" s="32" t="n"/>
-      <c r="I35" s="32" t="inlineStr">
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="28" t="n"/>
+      <c r="F35" s="28" t="n"/>
+      <c r="G35" s="39" t="n"/>
+      <c r="H35" s="23" t="n"/>
+      <c r="I35" s="23" t="inlineStr">
         <is>
           <t>if(${fts_result1}="Positive", "Positive",
     if(${fts_result1}="Invalid" and ${fts_result2}="Positive", "Positive", 
@@ -1972,815 +1959,815 @@
 	 )</t>
         </is>
       </c>
-      <c r="J35" s="33" t="inlineStr">
+      <c r="J35" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K35" s="33" t="n"/>
-      <c r="L35" s="33" t="n"/>
-      <c r="M35" s="33" t="n"/>
-      <c r="N35" s="33" t="inlineStr">
+      <c r="K35" s="28" t="n"/>
+      <c r="L35" s="28" t="n"/>
+      <c r="M35" s="28" t="n"/>
+      <c r="N35" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O35" s="33" t="n"/>
-      <c r="P35" s="33" t="n"/>
-      <c r="Q35" s="33" t="n"/>
-      <c r="R35" s="33" t="n"/>
-      <c r="S35" s="33" t="n"/>
-      <c r="T35" s="33" t="n"/>
+      <c r="O35" s="28" t="n"/>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n"/>
+      <c r="R35" s="28" t="n"/>
+      <c r="S35" s="28" t="n"/>
+      <c r="T35" s="28" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="31" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B36" s="33" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr">
         <is>
           <t>follow_up_note</t>
         </is>
       </c>
-      <c r="C36" s="34" t="inlineStr">
+      <c r="C36" s="29" t="inlineStr">
         <is>
           <t>Follow up form for positive cases</t>
         </is>
       </c>
-      <c r="D36" s="44" t="n"/>
-      <c r="E36" s="33" t="n"/>
-      <c r="F36" s="33" t="n"/>
-      <c r="G36" s="44" t="n"/>
-      <c r="H36" s="32" t="inlineStr">
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="28" t="n"/>
+      <c r="G36" s="39" t="n"/>
+      <c r="H36" s="23" t="inlineStr">
         <is>
           <t>${final_result} = 'Positive'</t>
         </is>
       </c>
-      <c r="I36" s="32" t="n"/>
-      <c r="J36" s="33" t="n"/>
-      <c r="K36" s="33" t="n"/>
-      <c r="L36" s="33" t="n"/>
-      <c r="M36" s="33" t="n"/>
-      <c r="N36" s="33" t="n"/>
-      <c r="O36" s="33" t="n"/>
-      <c r="P36" s="33" t="n"/>
-      <c r="Q36" s="33" t="n"/>
-      <c r="R36" s="33" t="n"/>
-      <c r="S36" s="33" t="n"/>
-      <c r="T36" s="33" t="n"/>
+      <c r="I36" s="23" t="n"/>
+      <c r="J36" s="28" t="n"/>
+      <c r="K36" s="28" t="n"/>
+      <c r="L36" s="28" t="n"/>
+      <c r="M36" s="28" t="n"/>
+      <c r="N36" s="28" t="n"/>
+      <c r="O36" s="28" t="n"/>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n"/>
+      <c r="R36" s="28" t="n"/>
+      <c r="S36" s="28" t="n"/>
+      <c r="T36" s="28" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="31" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="B37" s="33" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>lenght_stay_district</t>
         </is>
       </c>
-      <c r="C37" s="34" t="inlineStr">
+      <c r="C37" s="29" t="inlineStr">
         <is>
           <t>Number of years lived in this district</t>
         </is>
       </c>
-      <c r="D37" s="44" t="n"/>
-      <c r="E37" s="33" t="n"/>
-      <c r="F37" s="33" t="n"/>
-      <c r="G37" s="44" t="n"/>
-      <c r="H37" s="32" t="inlineStr">
+      <c r="D37" s="39" t="n"/>
+      <c r="E37" s="28" t="n"/>
+      <c r="F37" s="28" t="n"/>
+      <c r="G37" s="39" t="n"/>
+      <c r="H37" s="23" t="inlineStr">
         <is>
           <t>${final_result} = 'Positive'</t>
         </is>
       </c>
-      <c r="I37" s="32" t="n"/>
-      <c r="J37" s="33" t="inlineStr">
+      <c r="I37" s="23" t="n"/>
+      <c r="J37" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K37" s="33" t="n"/>
-      <c r="L37" s="33" t="n"/>
-      <c r="M37" s="33" t="n"/>
-      <c r="N37" s="33" t="n"/>
-      <c r="O37" s="33" t="n"/>
-      <c r="P37" s="33" t="n"/>
-      <c r="Q37" s="33" t="n"/>
-      <c r="R37" s="33" t="n"/>
-      <c r="S37" s="33" t="n"/>
-      <c r="T37" s="33" t="n"/>
+      <c r="K37" s="28" t="n"/>
+      <c r="L37" s="28" t="n"/>
+      <c r="M37" s="28" t="n"/>
+      <c r="N37" s="28" t="n"/>
+      <c r="O37" s="28" t="n"/>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n"/>
+      <c r="R37" s="28" t="n"/>
+      <c r="S37" s="28" t="n"/>
+      <c r="T37" s="28" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="31" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B38" s="33" t="inlineStr">
+      <c r="B38" s="28" t="inlineStr">
         <is>
           <t>village_origin</t>
         </is>
       </c>
-      <c r="C38" s="34" t="inlineStr">
+      <c r="C38" s="29" t="inlineStr">
         <is>
           <t>Village/Community or origin</t>
         </is>
       </c>
-      <c r="D38" s="44" t="n"/>
-      <c r="E38" s="33" t="n"/>
-      <c r="F38" s="33" t="n"/>
-      <c r="G38" s="44" t="n"/>
-      <c r="H38" s="32" t="inlineStr">
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="39" t="n"/>
+      <c r="H38" s="23" t="inlineStr">
         <is>
           <t>${final_result} = 'Positive'</t>
         </is>
       </c>
-      <c r="I38" s="32" t="n"/>
-      <c r="J38" s="33" t="inlineStr">
+      <c r="I38" s="23" t="n"/>
+      <c r="J38" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K38" s="33" t="n"/>
-      <c r="L38" s="33" t="n"/>
-      <c r="M38" s="33" t="n"/>
-      <c r="N38" s="33" t="n"/>
-      <c r="O38" s="33" t="n"/>
-      <c r="P38" s="33" t="n"/>
-      <c r="Q38" s="33" t="n"/>
-      <c r="R38" s="33" t="n"/>
-      <c r="S38" s="33" t="n"/>
-      <c r="T38" s="33" t="n"/>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="28" t="n"/>
+      <c r="M38" s="28" t="n"/>
+      <c r="N38" s="28" t="n"/>
+      <c r="O38" s="28" t="n"/>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n"/>
+      <c r="R38" s="28" t="n"/>
+      <c r="S38" s="28" t="n"/>
+      <c r="T38" s="28" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>select_one yes_no</t>
         </is>
       </c>
-      <c r="B39" s="33" t="inlineStr">
+      <c r="B39" s="28" t="inlineStr">
         <is>
           <t>swallowelf_med</t>
         </is>
       </c>
-      <c r="C39" s="34" t="inlineStr">
+      <c r="C39" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">Have you ever swallowed LF medicines </t>
         </is>
       </c>
-      <c r="D39" s="44" t="n"/>
-      <c r="E39" s="33" t="n"/>
-      <c r="F39" s="33" t="n"/>
-      <c r="G39" s="44" t="n"/>
-      <c r="H39" s="32" t="inlineStr">
+      <c r="D39" s="39" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="39" t="n"/>
+      <c r="H39" s="23" t="inlineStr">
         <is>
           <t>${final_result} = 'Positive'</t>
         </is>
       </c>
-      <c r="I39" s="32" t="n"/>
-      <c r="J39" s="33" t="inlineStr">
+      <c r="I39" s="23" t="n"/>
+      <c r="J39" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K39" s="33" t="n"/>
-      <c r="L39" s="33" t="n"/>
-      <c r="M39" s="33" t="n"/>
-      <c r="N39" s="33" t="n"/>
-      <c r="O39" s="33" t="n"/>
-      <c r="P39" s="33" t="n"/>
-      <c r="Q39" s="33" t="n"/>
-      <c r="R39" s="33" t="n"/>
-      <c r="S39" s="33" t="n"/>
-      <c r="T39" s="33" t="n"/>
+      <c r="K39" s="28" t="n"/>
+      <c r="L39" s="28" t="n"/>
+      <c r="M39" s="28" t="n"/>
+      <c r="N39" s="28" t="n"/>
+      <c r="O39" s="28" t="n"/>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n"/>
+      <c r="R39" s="28" t="n"/>
+      <c r="S39" s="28" t="n"/>
+      <c r="T39" s="28" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="31" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="B40" s="33" t="inlineStr">
+      <c r="B40" s="28" t="inlineStr">
         <is>
           <t>nmetaked</t>
         </is>
       </c>
-      <c r="C40" s="34" t="inlineStr">
+      <c r="C40" s="29" t="inlineStr">
         <is>
           <t>If Yes, how many times taken?</t>
         </is>
       </c>
-      <c r="D40" s="44" t="n"/>
-      <c r="E40" s="33" t="n"/>
-      <c r="F40" s="33" t="n"/>
-      <c r="G40" s="44" t="n"/>
-      <c r="H40" s="32" t="inlineStr">
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="39" t="n"/>
+      <c r="H40" s="23" t="inlineStr">
         <is>
           <t>${swallowelf_med} = 'Yes'</t>
         </is>
       </c>
-      <c r="I40" s="32" t="n"/>
-      <c r="J40" s="33" t="inlineStr">
+      <c r="I40" s="23" t="n"/>
+      <c r="J40" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K40" s="33" t="n"/>
-      <c r="L40" s="33" t="n"/>
-      <c r="M40" s="33" t="n"/>
-      <c r="N40" s="33" t="n"/>
-      <c r="O40" s="33" t="n"/>
-      <c r="P40" s="33" t="n"/>
-      <c r="Q40" s="33" t="n"/>
-      <c r="R40" s="33" t="n"/>
-      <c r="S40" s="33" t="n"/>
-      <c r="T40" s="33" t="n"/>
+      <c r="K40" s="28" t="n"/>
+      <c r="L40" s="28" t="n"/>
+      <c r="M40" s="28" t="n"/>
+      <c r="N40" s="28" t="n"/>
+      <c r="O40" s="28" t="n"/>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="28" t="n"/>
+      <c r="R40" s="28" t="n"/>
+      <c r="S40" s="28" t="n"/>
+      <c r="T40" s="28" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>select_one yes_no</t>
         </is>
       </c>
-      <c r="B41" s="33" t="inlineStr">
+      <c r="B41" s="28" t="inlineStr">
         <is>
           <t>have_benet</t>
         </is>
       </c>
-      <c r="C41" s="34" t="inlineStr">
+      <c r="C41" s="29" t="inlineStr">
         <is>
           <t>Do you have mosquito net?</t>
         </is>
       </c>
-      <c r="D41" s="44" t="n"/>
-      <c r="E41" s="33" t="n"/>
-      <c r="F41" s="33" t="n"/>
-      <c r="G41" s="44" t="n"/>
-      <c r="H41" s="32" t="inlineStr">
+      <c r="D41" s="39" t="n"/>
+      <c r="E41" s="28" t="n"/>
+      <c r="F41" s="28" t="n"/>
+      <c r="G41" s="39" t="n"/>
+      <c r="H41" s="23" t="inlineStr">
         <is>
           <t>${final_result} = 'Positive'</t>
         </is>
       </c>
-      <c r="I41" s="32" t="n"/>
-      <c r="J41" s="33" t="inlineStr">
+      <c r="I41" s="23" t="n"/>
+      <c r="J41" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K41" s="33" t="n"/>
-      <c r="L41" s="33" t="n"/>
-      <c r="M41" s="33" t="n"/>
-      <c r="N41" s="33" t="n"/>
-      <c r="O41" s="33" t="n"/>
-      <c r="P41" s="33" t="n"/>
-      <c r="Q41" s="33" t="n"/>
-      <c r="R41" s="33" t="n"/>
-      <c r="S41" s="33" t="n"/>
-      <c r="T41" s="33" t="n"/>
+      <c r="K41" s="28" t="n"/>
+      <c r="L41" s="28" t="n"/>
+      <c r="M41" s="28" t="n"/>
+      <c r="N41" s="28" t="n"/>
+      <c r="O41" s="28" t="n"/>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="28" t="n"/>
+      <c r="R41" s="28" t="n"/>
+      <c r="S41" s="28" t="n"/>
+      <c r="T41" s="28" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="31" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>select_one yes_no</t>
         </is>
       </c>
-      <c r="B42" s="33" t="inlineStr">
+      <c r="B42" s="28" t="inlineStr">
         <is>
           <t>sleep_benet</t>
         </is>
       </c>
-      <c r="C42" s="34" t="inlineStr">
+      <c r="C42" s="29" t="inlineStr">
         <is>
           <t>Do you sleep inside mosquito net?</t>
         </is>
       </c>
-      <c r="D42" s="44" t="n"/>
-      <c r="E42" s="33" t="n"/>
-      <c r="F42" s="33" t="n"/>
-      <c r="G42" s="44" t="n"/>
-      <c r="H42" s="32" t="inlineStr">
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="39" t="n"/>
+      <c r="H42" s="23" t="inlineStr">
         <is>
           <t>${have_benet} = 'Yes'</t>
         </is>
       </c>
-      <c r="I42" s="32" t="n"/>
-      <c r="J42" s="33" t="inlineStr">
+      <c r="I42" s="23" t="n"/>
+      <c r="J42" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K42" s="33" t="n"/>
-      <c r="L42" s="33" t="n"/>
-      <c r="M42" s="33" t="n"/>
-      <c r="N42" s="33" t="n"/>
-      <c r="O42" s="33" t="n"/>
-      <c r="P42" s="33" t="n"/>
-      <c r="Q42" s="33" t="n"/>
-      <c r="R42" s="33" t="n"/>
-      <c r="S42" s="33" t="n"/>
-      <c r="T42" s="33" t="n"/>
-    </row>
-    <row r="43" ht="47.25" customHeight="1">
-      <c r="A43" s="31" t="inlineStr">
+      <c r="K42" s="28" t="n"/>
+      <c r="L42" s="28" t="n"/>
+      <c r="M42" s="28" t="n"/>
+      <c r="N42" s="28" t="n"/>
+      <c r="O42" s="28" t="n"/>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="28" t="n"/>
+      <c r="R42" s="28" t="n"/>
+      <c r="S42" s="28" t="n"/>
+      <c r="T42" s="28" t="n"/>
+    </row>
+    <row r="43" ht="46.5" customHeight="1">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B43" s="33" t="inlineStr">
+      <c r="B43" s="28" t="inlineStr">
         <is>
           <t>mf_note</t>
         </is>
       </c>
-      <c r="C43" s="34" t="inlineStr">
+      <c r="C43" s="29" t="inlineStr">
         <is>
           <t>This participant's FTS test result is POSITIVE, requiring a Night Blood Test for microfilariae (Mf). Continue below to record the Mf test result.</t>
         </is>
       </c>
-      <c r="D43" s="44" t="n"/>
-      <c r="E43" s="33" t="n"/>
-      <c r="F43" s="33" t="n"/>
-      <c r="G43" s="44" t="n"/>
-      <c r="H43" s="32" t="inlineStr">
+      <c r="D43" s="39" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="39" t="n"/>
+      <c r="H43" s="23" t="inlineStr">
         <is>
           <t>(${fts_result1} = 'Positive' or ${fts_result2} = 'Positive')</t>
         </is>
       </c>
-      <c r="I43" s="31" t="n"/>
-      <c r="J43" s="33" t="n"/>
-      <c r="K43" s="33" t="n"/>
-      <c r="L43" s="33" t="n"/>
-      <c r="M43" s="33" t="n"/>
-      <c r="N43" s="33" t="n"/>
-      <c r="O43" s="33" t="n"/>
-      <c r="P43" s="33" t="n"/>
-      <c r="Q43" s="33" t="n"/>
-      <c r="R43" s="33" t="n"/>
-      <c r="S43" s="33" t="n"/>
-      <c r="T43" s="33" t="n"/>
-    </row>
-    <row r="44" ht="31.5" customHeight="1">
-      <c r="A44" s="31" t="inlineStr">
+      <c r="I43" s="21" t="n"/>
+      <c r="J43" s="28" t="n"/>
+      <c r="K43" s="28" t="n"/>
+      <c r="L43" s="28" t="n"/>
+      <c r="M43" s="28" t="n"/>
+      <c r="N43" s="28" t="n"/>
+      <c r="O43" s="28" t="n"/>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="28" t="n"/>
+      <c r="R43" s="28" t="n"/>
+      <c r="S43" s="28" t="n"/>
+      <c r="T43" s="28" t="n"/>
+    </row>
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B44" s="33" t="inlineStr">
+      <c r="B44" s="28" t="inlineStr">
         <is>
           <t>mf_date</t>
         </is>
       </c>
-      <c r="C44" s="34" t="inlineStr">
+      <c r="C44" s="29" t="inlineStr">
         <is>
           <t>Mf test : Date of blood collection</t>
         </is>
       </c>
-      <c r="D44" s="44" t="n"/>
-      <c r="E44" s="33" t="n"/>
-      <c r="F44" s="33" t="n"/>
-      <c r="G44" s="44" t="n"/>
-      <c r="H44" s="32" t="inlineStr">
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="39" t="n"/>
+      <c r="H44" s="23" t="inlineStr">
         <is>
           <t>(${fts_result1} = 'Positive' or ${fts_result2} = 'Positive')</t>
         </is>
       </c>
-      <c r="I44" s="31" t="n"/>
-      <c r="J44" s="33" t="inlineStr">
+      <c r="I44" s="21" t="n"/>
+      <c r="J44" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K44" s="33" t="n"/>
-      <c r="L44" s="33" t="n"/>
-      <c r="M44" s="33" t="n"/>
-      <c r="N44" s="33" t="n"/>
-      <c r="O44" s="33" t="n"/>
-      <c r="P44" s="33" t="n"/>
-      <c r="Q44" s="33" t="n"/>
-      <c r="R44" s="33" t="n"/>
-      <c r="S44" s="33" t="n"/>
-      <c r="T44" s="33" t="n"/>
-    </row>
-    <row r="45" ht="31.5" customHeight="1">
-      <c r="A45" s="31" t="inlineStr">
+      <c r="K44" s="28" t="n"/>
+      <c r="L44" s="28" t="n"/>
+      <c r="M44" s="28" t="n"/>
+      <c r="N44" s="28" t="n"/>
+      <c r="O44" s="28" t="n"/>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="28" t="n"/>
+      <c r="R44" s="28" t="n"/>
+      <c r="S44" s="28" t="n"/>
+      <c r="T44" s="28" t="n"/>
+    </row>
+    <row r="45" ht="31" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>select_one time</t>
         </is>
       </c>
-      <c r="B45" s="33" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>mf_time</t>
         </is>
       </c>
-      <c r="C45" s="34" t="inlineStr">
+      <c r="C45" s="29" t="inlineStr">
         <is>
           <t>Mf test : Time of blood collection</t>
         </is>
       </c>
-      <c r="D45" s="44" t="n"/>
-      <c r="E45" s="33" t="n"/>
-      <c r="F45" s="33" t="n"/>
-      <c r="G45" s="44" t="n"/>
-      <c r="H45" s="32" t="inlineStr">
+      <c r="D45" s="39" t="n"/>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="39" t="n"/>
+      <c r="H45" s="23" t="inlineStr">
         <is>
           <t>(${fts_result1} = 'Positive' or ${fts_result2} = 'Positive')</t>
         </is>
       </c>
-      <c r="I45" s="33" t="n"/>
-      <c r="J45" s="33" t="inlineStr">
+      <c r="I45" s="28" t="n"/>
+      <c r="J45" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K45" s="33" t="n"/>
-      <c r="L45" s="33" t="n"/>
-      <c r="M45" s="33" t="n"/>
-      <c r="N45" s="33" t="n"/>
-      <c r="O45" s="33" t="n"/>
-      <c r="P45" s="33" t="n"/>
-      <c r="Q45" s="33" t="n"/>
-      <c r="R45" s="33" t="n"/>
-      <c r="S45" s="33" t="n"/>
-      <c r="T45" s="33" t="n"/>
-    </row>
-    <row r="46" ht="31.5" customHeight="1">
-      <c r="A46" s="31" t="inlineStr">
+      <c r="K45" s="28" t="n"/>
+      <c r="L45" s="28" t="n"/>
+      <c r="M45" s="28" t="n"/>
+      <c r="N45" s="28" t="n"/>
+      <c r="O45" s="28" t="n"/>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="28" t="n"/>
+      <c r="R45" s="28" t="n"/>
+      <c r="S45" s="28" t="n"/>
+      <c r="T45" s="28" t="n"/>
+    </row>
+    <row r="46" ht="31" customHeight="1">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="B46" s="33" t="inlineStr">
+      <c r="B46" s="28" t="inlineStr">
         <is>
           <t>bloovol_microL</t>
         </is>
       </c>
-      <c r="C46" s="34" t="inlineStr">
+      <c r="C46" s="29" t="inlineStr">
         <is>
           <t>Blood volume collected (µL)</t>
         </is>
       </c>
-      <c r="D46" s="44" t="n"/>
-      <c r="E46" s="33" t="n"/>
-      <c r="F46" s="33" t="n"/>
-      <c r="G46" s="44" t="n"/>
-      <c r="H46" s="32" t="inlineStr">
+      <c r="D46" s="39" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
+      <c r="G46" s="39" t="n"/>
+      <c r="H46" s="23" t="inlineStr">
         <is>
           <t>(${fts_result1} = 'Positive' or ${fts_result2} = 'Positive')</t>
         </is>
       </c>
-      <c r="I46" s="33" t="n"/>
-      <c r="J46" s="33" t="inlineStr">
+      <c r="I46" s="28" t="n"/>
+      <c r="J46" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K46" s="33" t="n"/>
-      <c r="L46" s="33" t="n"/>
-      <c r="M46" s="33" t="n"/>
-      <c r="N46" s="33" t="n"/>
-      <c r="O46" s="33" t="n"/>
-      <c r="P46" s="33" t="n"/>
-      <c r="Q46" s="33" t="n"/>
-      <c r="R46" s="33" t="n"/>
-      <c r="S46" s="33" t="n"/>
-      <c r="T46" s="33" t="n"/>
-    </row>
-    <row r="47" ht="31.5" customHeight="1">
-      <c r="A47" s="31" t="inlineStr">
+      <c r="K46" s="28" t="n"/>
+      <c r="L46" s="28" t="n"/>
+      <c r="M46" s="28" t="n"/>
+      <c r="N46" s="28" t="n"/>
+      <c r="O46" s="28" t="n"/>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="28" t="n"/>
+      <c r="R46" s="28" t="n"/>
+      <c r="S46" s="28" t="n"/>
+      <c r="T46" s="28" t="n"/>
+    </row>
+    <row r="47" ht="31" customHeight="1">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>select_one mf_result</t>
         </is>
       </c>
-      <c r="B47" s="33" t="inlineStr">
+      <c r="B47" s="28" t="inlineStr">
         <is>
           <t>mf_result</t>
         </is>
       </c>
-      <c r="C47" s="34" t="inlineStr">
+      <c r="C47" s="29" t="inlineStr">
         <is>
           <t>Mf test result</t>
         </is>
       </c>
-      <c r="D47" s="44" t="n"/>
-      <c r="E47" s="33" t="n"/>
-      <c r="F47" s="33" t="n"/>
-      <c r="G47" s="44" t="n"/>
-      <c r="H47" s="32" t="inlineStr">
+      <c r="D47" s="39" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="39" t="n"/>
+      <c r="H47" s="23" t="inlineStr">
         <is>
           <t>(${fts_result1} = 'Positive' or ${fts_result2} = 'Positive')</t>
         </is>
       </c>
-      <c r="I47" s="33" t="n"/>
-      <c r="J47" s="33" t="inlineStr">
+      <c r="I47" s="28" t="n"/>
+      <c r="J47" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K47" s="33" t="n"/>
-      <c r="L47" s="33" t="n"/>
-      <c r="M47" s="33" t="n"/>
-      <c r="N47" s="33" t="n"/>
-      <c r="O47" s="33" t="n"/>
-      <c r="P47" s="33" t="n"/>
-      <c r="Q47" s="33" t="n"/>
-      <c r="R47" s="33" t="n"/>
-      <c r="S47" s="33" t="n"/>
-      <c r="T47" s="33" t="n"/>
-    </row>
-    <row r="48" ht="31.5" customHeight="1">
-      <c r="A48" s="31" t="inlineStr">
+      <c r="K47" s="28" t="n"/>
+      <c r="L47" s="28" t="n"/>
+      <c r="M47" s="28" t="n"/>
+      <c r="N47" s="28" t="n"/>
+      <c r="O47" s="28" t="n"/>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="28" t="n"/>
+      <c r="R47" s="28" t="n"/>
+      <c r="S47" s="28" t="n"/>
+      <c r="T47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="31" customHeight="1">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="B48" s="33" t="inlineStr">
+      <c r="B48" s="28" t="inlineStr">
         <is>
           <t>mf_per_60microL</t>
         </is>
       </c>
-      <c r="C48" s="34" t="inlineStr">
+      <c r="C48" s="29" t="inlineStr">
         <is>
           <t>Mf count per 60 µL :</t>
         </is>
       </c>
-      <c r="D48" s="44" t="n"/>
-      <c r="E48" s="33" t="n"/>
-      <c r="F48" s="33" t="n"/>
-      <c r="G48" s="44" t="n"/>
-      <c r="H48" s="32" t="inlineStr">
+      <c r="D48" s="39" t="n"/>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="28" t="n"/>
+      <c r="G48" s="39" t="n"/>
+      <c r="H48" s="23" t="inlineStr">
         <is>
           <t>(${fts_result1} = 'Positive' or ${fts_result2} = 'Positive') and ${mf_result} = 'Positive'</t>
         </is>
       </c>
-      <c r="I48" s="33" t="n"/>
-      <c r="J48" s="33" t="inlineStr">
+      <c r="I48" s="28" t="n"/>
+      <c r="J48" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K48" s="33" t="n"/>
-      <c r="L48" s="33" t="n"/>
-      <c r="M48" s="33" t="n"/>
-      <c r="N48" s="33" t="n"/>
-      <c r="O48" s="33" t="n"/>
-      <c r="P48" s="33" t="n"/>
-      <c r="Q48" s="33" t="n"/>
-      <c r="R48" s="33" t="n"/>
-      <c r="S48" s="33" t="n"/>
-      <c r="T48" s="33" t="n"/>
-    </row>
-    <row r="49" ht="31.5" customHeight="1">
-      <c r="A49" s="31" t="inlineStr">
+      <c r="K48" s="28" t="n"/>
+      <c r="L48" s="28" t="n"/>
+      <c r="M48" s="28" t="n"/>
+      <c r="N48" s="28" t="n"/>
+      <c r="O48" s="28" t="n"/>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="28" t="n"/>
+      <c r="R48" s="28" t="n"/>
+      <c r="S48" s="28" t="n"/>
+      <c r="T48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="31" customHeight="1">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>select_multiple mf_species</t>
         </is>
       </c>
-      <c r="B49" s="33" t="inlineStr">
+      <c r="B49" s="28" t="inlineStr">
         <is>
           <t>mf_species</t>
         </is>
       </c>
-      <c r="C49" s="34" t="inlineStr">
+      <c r="C49" s="29" t="inlineStr">
         <is>
           <t>Species identified :</t>
         </is>
       </c>
-      <c r="D49" s="44" t="n"/>
-      <c r="E49" s="33" t="n"/>
-      <c r="F49" s="33" t="n"/>
-      <c r="G49" s="44" t="n"/>
-      <c r="H49" s="32" t="inlineStr">
+      <c r="D49" s="39" t="n"/>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="28" t="n"/>
+      <c r="G49" s="39" t="n"/>
+      <c r="H49" s="23" t="inlineStr">
         <is>
           <t>(${fts_result1} = 'Positive' or ${fts_result2} = 'Positive') and ${mf_result} = 'Positive'</t>
         </is>
       </c>
-      <c r="I49" s="33" t="n"/>
-      <c r="J49" s="33" t="inlineStr">
+      <c r="I49" s="28" t="n"/>
+      <c r="J49" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K49" s="33" t="n"/>
-      <c r="L49" s="33" t="n"/>
-      <c r="M49" s="33" t="n"/>
-      <c r="N49" s="33" t="n"/>
-      <c r="O49" s="33" t="n"/>
-      <c r="P49" s="33" t="n"/>
-      <c r="Q49" s="33" t="n"/>
-      <c r="R49" s="33" t="n"/>
-      <c r="S49" s="33" t="n"/>
-      <c r="T49" s="33" t="n"/>
+      <c r="K49" s="28" t="n"/>
+      <c r="L49" s="28" t="n"/>
+      <c r="M49" s="28" t="n"/>
+      <c r="N49" s="28" t="n"/>
+      <c r="O49" s="28" t="n"/>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="28" t="n"/>
+      <c r="R49" s="28" t="n"/>
+      <c r="S49" s="28" t="n"/>
+      <c r="T49" s="28" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="31" t="inlineStr">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B50" s="33" t="inlineStr">
+      <c r="B50" s="28" t="inlineStr">
         <is>
           <t>mf_species_other</t>
         </is>
       </c>
-      <c r="C50" s="34" t="inlineStr">
+      <c r="C50" s="29" t="inlineStr">
         <is>
           <t>Please specify :</t>
         </is>
       </c>
-      <c r="D50" s="44" t="n"/>
-      <c r="E50" s="33" t="n"/>
-      <c r="F50" s="33" t="n"/>
-      <c r="G50" s="44" t="n"/>
-      <c r="H50" s="32" t="inlineStr">
+      <c r="D50" s="39" t="n"/>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="28" t="n"/>
+      <c r="G50" s="39" t="n"/>
+      <c r="H50" s="23" t="inlineStr">
         <is>
           <t>selected(${mf_species}, 'Other')</t>
         </is>
       </c>
-      <c r="I50" s="33" t="n"/>
-      <c r="J50" s="33" t="inlineStr">
+      <c r="I50" s="28" t="n"/>
+      <c r="J50" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K50" s="33" t="n"/>
-      <c r="L50" s="33" t="n"/>
-      <c r="M50" s="33" t="n"/>
-      <c r="N50" s="33" t="n"/>
-      <c r="O50" s="33" t="n"/>
-      <c r="P50" s="33" t="n"/>
-      <c r="Q50" s="33" t="n"/>
-      <c r="R50" s="33" t="n"/>
-      <c r="S50" s="33" t="n"/>
-      <c r="T50" s="33" t="n"/>
+      <c r="K50" s="28" t="n"/>
+      <c r="L50" s="28" t="n"/>
+      <c r="M50" s="28" t="n"/>
+      <c r="N50" s="28" t="n"/>
+      <c r="O50" s="28" t="n"/>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="28" t="n"/>
+      <c r="R50" s="28" t="n"/>
+      <c r="S50" s="28" t="n"/>
+      <c r="T50" s="28" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="31" t="n"/>
-      <c r="B51" s="33" t="n"/>
-      <c r="C51" s="34" t="n"/>
-      <c r="D51" s="44" t="n"/>
-      <c r="E51" s="33" t="n"/>
-      <c r="F51" s="33" t="n"/>
-      <c r="G51" s="44" t="n"/>
-      <c r="H51" s="32" t="n"/>
-      <c r="I51" s="33" t="n"/>
-      <c r="J51" s="33" t="n"/>
-      <c r="K51" s="33" t="n"/>
-      <c r="L51" s="33" t="n"/>
-      <c r="M51" s="33" t="n"/>
-      <c r="N51" s="33" t="n"/>
-      <c r="O51" s="33" t="n"/>
-      <c r="P51" s="33" t="n"/>
-      <c r="Q51" s="33" t="n"/>
-      <c r="R51" s="33" t="n"/>
-      <c r="S51" s="33" t="n"/>
-      <c r="T51" s="33" t="n"/>
+      <c r="A51" s="21" t="n"/>
+      <c r="B51" s="28" t="n"/>
+      <c r="C51" s="29" t="n"/>
+      <c r="D51" s="39" t="n"/>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="28" t="n"/>
+      <c r="G51" s="39" t="n"/>
+      <c r="H51" s="23" t="n"/>
+      <c r="I51" s="28" t="n"/>
+      <c r="J51" s="28" t="n"/>
+      <c r="K51" s="28" t="n"/>
+      <c r="L51" s="28" t="n"/>
+      <c r="M51" s="28" t="n"/>
+      <c r="N51" s="28" t="n"/>
+      <c r="O51" s="28" t="n"/>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="28" t="n"/>
+      <c r="R51" s="28" t="n"/>
+      <c r="S51" s="28" t="n"/>
+      <c r="T51" s="28" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="31" t="inlineStr">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B52" s="33" t="inlineStr">
+      <c r="B52" s="28" t="inlineStr">
         <is>
           <t>comments</t>
         </is>
       </c>
-      <c r="C52" s="34" t="inlineStr">
+      <c r="C52" s="29" t="inlineStr">
         <is>
           <t>Additional Notes</t>
         </is>
       </c>
-      <c r="D52" s="44" t="n"/>
-      <c r="E52" s="33" t="n"/>
-      <c r="F52" s="33" t="n"/>
-      <c r="G52" s="44" t="n"/>
-      <c r="H52" s="45" t="n"/>
-      <c r="I52" s="33" t="n"/>
-      <c r="J52" s="33" t="n"/>
-      <c r="K52" s="33" t="n"/>
-      <c r="L52" s="33" t="n"/>
-      <c r="M52" s="33" t="n"/>
-      <c r="N52" s="33" t="n"/>
-      <c r="O52" s="36" t="inlineStr">
+      <c r="D52" s="39" t="n"/>
+      <c r="E52" s="28" t="n"/>
+      <c r="F52" s="28" t="n"/>
+      <c r="G52" s="39" t="n"/>
+      <c r="H52" s="40" t="n"/>
+      <c r="I52" s="28" t="n"/>
+      <c r="J52" s="28" t="n"/>
+      <c r="K52" s="28" t="n"/>
+      <c r="L52" s="28" t="n"/>
+      <c r="M52" s="28" t="n"/>
+      <c r="N52" s="28" t="n"/>
+      <c r="O52" s="31" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="P52" s="33" t="n"/>
-      <c r="Q52" s="33" t="n"/>
-      <c r="R52" s="33" t="n"/>
-      <c r="S52" s="33" t="n"/>
-      <c r="T52" s="33" t="n"/>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="28" t="n"/>
+      <c r="R52" s="28" t="n"/>
+      <c r="S52" s="28" t="n"/>
+      <c r="T52" s="28" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="32" t="inlineStr">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t>end repeat</t>
         </is>
       </c>
-      <c r="B53" s="33" t="n"/>
-      <c r="C53" s="34" t="n"/>
-      <c r="D53" s="44" t="n"/>
-      <c r="E53" s="33" t="n"/>
-      <c r="F53" s="33" t="n"/>
-      <c r="G53" s="44" t="n"/>
-      <c r="H53" s="45" t="n"/>
-      <c r="I53" s="33" t="n"/>
-      <c r="J53" s="33" t="n"/>
-      <c r="K53" s="33" t="n"/>
-      <c r="L53" s="33" t="n"/>
-      <c r="M53" s="33" t="n"/>
-      <c r="N53" s="33" t="n"/>
-      <c r="O53" s="33" t="n"/>
-      <c r="P53" s="33" t="n"/>
-      <c r="Q53" s="33" t="n"/>
-      <c r="R53" s="33" t="n"/>
-      <c r="S53" s="33" t="n"/>
-      <c r="T53" s="33" t="n"/>
+      <c r="B53" s="28" t="n"/>
+      <c r="C53" s="29" t="n"/>
+      <c r="D53" s="39" t="n"/>
+      <c r="E53" s="28" t="n"/>
+      <c r="F53" s="28" t="n"/>
+      <c r="G53" s="39" t="n"/>
+      <c r="H53" s="40" t="n"/>
+      <c r="I53" s="28" t="n"/>
+      <c r="J53" s="28" t="n"/>
+      <c r="K53" s="28" t="n"/>
+      <c r="L53" s="28" t="n"/>
+      <c r="M53" s="28" t="n"/>
+      <c r="N53" s="28" t="n"/>
+      <c r="O53" s="28" t="n"/>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="28" t="n"/>
+      <c r="R53" s="28" t="n"/>
+      <c r="S53" s="28" t="n"/>
+      <c r="T53" s="28" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="31" t="n"/>
-      <c r="B54" s="33" t="n"/>
-      <c r="C54" s="34" t="n"/>
-      <c r="D54" s="44" t="n"/>
-      <c r="E54" s="33" t="n"/>
-      <c r="F54" s="33" t="n"/>
-      <c r="G54" s="44" t="n"/>
-      <c r="H54" s="45" t="n"/>
-      <c r="I54" s="33" t="n"/>
-      <c r="J54" s="33" t="n"/>
-      <c r="K54" s="33" t="n"/>
-      <c r="L54" s="33" t="n"/>
-      <c r="M54" s="33" t="n"/>
-      <c r="N54" s="33" t="n"/>
-      <c r="O54" s="33" t="n"/>
-      <c r="P54" s="33" t="n"/>
-      <c r="Q54" s="33" t="n"/>
-      <c r="R54" s="33" t="n"/>
-      <c r="S54" s="33" t="n"/>
-      <c r="T54" s="33" t="n"/>
+      <c r="A54" s="21" t="n"/>
+      <c r="B54" s="28" t="n"/>
+      <c r="C54" s="29" t="n"/>
+      <c r="D54" s="39" t="n"/>
+      <c r="E54" s="28" t="n"/>
+      <c r="F54" s="28" t="n"/>
+      <c r="G54" s="39" t="n"/>
+      <c r="H54" s="40" t="n"/>
+      <c r="I54" s="28" t="n"/>
+      <c r="J54" s="28" t="n"/>
+      <c r="K54" s="28" t="n"/>
+      <c r="L54" s="28" t="n"/>
+      <c r="M54" s="28" t="n"/>
+      <c r="N54" s="28" t="n"/>
+      <c r="O54" s="28" t="n"/>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="28" t="n"/>
+      <c r="R54" s="28" t="n"/>
+      <c r="S54" s="28" t="n"/>
+      <c r="T54" s="28" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="31" t="inlineStr">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B55" s="33" t="inlineStr">
+      <c r="B55" s="28" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="C55" s="34" t="n"/>
-      <c r="D55" s="44" t="n"/>
-      <c r="E55" s="33" t="n"/>
-      <c r="F55" s="33" t="n"/>
-      <c r="G55" s="44" t="n"/>
-      <c r="H55" s="45" t="n"/>
-      <c r="I55" s="33" t="n"/>
-      <c r="J55" s="33" t="n"/>
-      <c r="K55" s="33" t="n"/>
-      <c r="L55" s="33" t="n"/>
-      <c r="M55" s="33" t="n"/>
-      <c r="N55" s="33" t="n"/>
-      <c r="O55" s="33" t="n"/>
-      <c r="P55" s="33" t="n"/>
-      <c r="Q55" s="33" t="n"/>
-      <c r="R55" s="33" t="n"/>
-      <c r="S55" s="33" t="n"/>
-      <c r="T55" s="33" t="n"/>
+      <c r="C55" s="29" t="n"/>
+      <c r="D55" s="39" t="n"/>
+      <c r="E55" s="28" t="n"/>
+      <c r="F55" s="28" t="n"/>
+      <c r="G55" s="39" t="n"/>
+      <c r="H55" s="40" t="n"/>
+      <c r="I55" s="28" t="n"/>
+      <c r="J55" s="28" t="n"/>
+      <c r="K55" s="28" t="n"/>
+      <c r="L55" s="28" t="n"/>
+      <c r="M55" s="28" t="n"/>
+      <c r="N55" s="28" t="n"/>
+      <c r="O55" s="28" t="n"/>
+      <c r="P55" s="28" t="n"/>
+      <c r="Q55" s="28" t="n"/>
+      <c r="R55" s="28" t="n"/>
+      <c r="S55" s="28" t="n"/>
+      <c r="T55" s="28" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="31" t="inlineStr">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B56" s="33" t="inlineStr">
+      <c r="B56" s="28" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C56" s="34" t="n"/>
-      <c r="D56" s="44" t="n"/>
-      <c r="E56" s="33" t="n"/>
-      <c r="F56" s="33" t="n"/>
-      <c r="G56" s="44" t="n"/>
-      <c r="H56" s="45" t="n"/>
-      <c r="I56" s="33" t="n"/>
-      <c r="J56" s="33" t="n"/>
-      <c r="K56" s="33" t="n"/>
-      <c r="L56" s="33" t="n"/>
-      <c r="M56" s="33" t="n"/>
-      <c r="N56" s="33" t="n"/>
-      <c r="O56" s="33" t="n"/>
-      <c r="P56" s="33" t="n"/>
-      <c r="Q56" s="33" t="n"/>
-      <c r="R56" s="33" t="n"/>
-      <c r="S56" s="33" t="n"/>
-      <c r="T56" s="33" t="n"/>
+      <c r="C56" s="29" t="n"/>
+      <c r="D56" s="39" t="n"/>
+      <c r="E56" s="28" t="n"/>
+      <c r="F56" s="28" t="n"/>
+      <c r="G56" s="39" t="n"/>
+      <c r="H56" s="40" t="n"/>
+      <c r="I56" s="28" t="n"/>
+      <c r="J56" s="28" t="n"/>
+      <c r="K56" s="28" t="n"/>
+      <c r="L56" s="28" t="n"/>
+      <c r="M56" s="28" t="n"/>
+      <c r="N56" s="28" t="n"/>
+      <c r="O56" s="28" t="n"/>
+      <c r="P56" s="28" t="n"/>
+      <c r="Q56" s="28" t="n"/>
+      <c r="R56" s="28" t="n"/>
+      <c r="S56" s="28" t="n"/>
+      <c r="T56" s="28" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2795,26 +2782,26 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G42"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
-    <col width="16.375" customWidth="1" style="8" min="1" max="1"/>
-    <col width="61" customWidth="1" style="8" min="2" max="2"/>
-    <col width="34" customWidth="1" style="8" min="3" max="3"/>
-    <col width="11" customWidth="1" style="8" min="4" max="16384"/>
+    <col width="16.33203125" customWidth="1" style="5" min="1" max="1"/>
+    <col width="61" customWidth="1" style="5" min="2" max="2"/>
+    <col width="34" customWidth="1" style="5" min="3" max="3"/>
+    <col width="11" customWidth="1" style="5" min="4" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="8">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>list_name</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>label::English (en)</t>
         </is>
@@ -2834,369 +2821,369 @@
           <t>site</t>
         </is>
       </c>
-      <c r="G1" s="4" t="n"/>
-    </row>
-    <row r="2" customFormat="1" s="8">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
-      <c r="G2" s="4" t="n"/>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="48" t="inlineStr">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>yes_no</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C3" s="46" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>yes_no</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C4" s="46" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="n"/>
-      <c r="C5" s="46" t="n"/>
+      <c r="A5" s="43" t="n"/>
+      <c r="C5" s="41" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>warning_note</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Understood</t>
         </is>
       </c>
-      <c r="C6" s="46" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>I have read and understood</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="n"/>
-      <c r="C7" s="46" t="n"/>
+      <c r="A7" s="43" t="n"/>
+      <c r="C7" s="41" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>results_list</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C8" s="46" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>results_list</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C9" s="46" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Negative </t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>results_list</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Invalid</t>
         </is>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C10" s="41" t="inlineStr">
         <is>
           <t>Invalid</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="46" t="n"/>
+      <c r="C11" s="41" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Absence.of.control.line</t>
         </is>
       </c>
-      <c r="C12" s="46" t="inlineStr">
+      <c r="C12" s="41" t="inlineStr">
         <is>
           <t>Absence of control line</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Broken/partial.control.line</t>
         </is>
       </c>
-      <c r="C13" s="46" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <t>Broken/partial control line</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Difficulty.of.absorbing.sample</t>
         </is>
       </c>
-      <c r="C14" s="46" t="inlineStr">
+      <c r="C14" s="41" t="inlineStr">
         <is>
           <t>Difficulty of absorbing sample</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Difficulty.of.migrating.sample</t>
         </is>
       </c>
-      <c r="C15" s="46" t="inlineStr">
+      <c r="C15" s="41" t="inlineStr">
         <is>
           <t>Difficulty of migrating sample</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Trace.of.blood.persists</t>
         </is>
       </c>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" s="41" t="inlineStr">
         <is>
           <t>Trace of blood persists</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Insufficient.blood.volume.due.to.pipette</t>
         </is>
       </c>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C17" s="41" t="inlineStr">
         <is>
           <t>Insufficient blood volume due to pipette</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>why_invalid</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C18" s="46" t="inlineStr">
+      <c r="C18" s="41" t="inlineStr">
         <is>
           <t>Other (pleas explain)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="46" t="n"/>
-    </row>
-    <row r="20" customFormat="1" s="8">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="C19" s="41" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>recorder_list</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
     </row>
-    <row r="21" customFormat="1" s="8">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>recorder_list</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
     </row>
-    <row r="22" customFormat="1" s="8">
-      <c r="A22" s="17" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>recorder_list</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
     </row>
-    <row r="23" customFormat="1" s="8">
-      <c r="A23" s="17" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>recorder_list</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
     </row>
-    <row r="24" customFormat="1" s="8">
-      <c r="A24" s="20" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>recorder_list</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="15" t="n">
         <v>99</v>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>99 (For testing and training only)</t>
         </is>
       </c>
     </row>
-    <row r="25" customFormat="1" s="8">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="49" t="n"/>
-      <c r="C25" s="49" t="n"/>
-    </row>
-    <row r="26" customFormat="1" s="8">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="44" t="n"/>
+      <c r="C25" s="44" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>barcode_method</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>QRScann</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Scan the QR/barcode using the device</t>
         </is>
       </c>
     </row>
-    <row r="27" customFormat="1" s="8">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>barcode_method</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>QRManual</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Manual entry (if scanner fails)</t>
         </is>
@@ -3204,34 +3191,34 @@
     </row>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>id_type</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>ID_generation</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>ID Codes generated (from the participant form)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>id_type</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Scanner</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Scanner (QR Codes/Barcodes)</t>
         </is>
@@ -3239,85 +3226,85 @@
     </row>
     <row r="31"/>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>21:00–22:00</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>21:00–22:00</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>22:00–23:00</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>22:00–23:00</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>23:00–00:00</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>23:00–00:00</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>00:00–01:00</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>00:00–01:00</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>01:00–02:00</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>01:00–02:00</t>
         </is>
@@ -3325,34 +3312,34 @@
     </row>
     <row r="37"/>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>mf_result</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>mf_result</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -3360,34 +3347,34 @@
     </row>
     <row r="40"/>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>mf_species</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Wuchereria_bancrofti</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Wuchereria bancrofti</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>mf_species</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Other (Specify)</t>
         </is>
@@ -3405,15 +3392,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
-    <col width="46.625" customWidth="1" min="1" max="1"/>
-    <col width="34.125" customWidth="1" min="2" max="2"/>
-    <col width="15.875" customWidth="1" min="3" max="3"/>
+    <col width="46.58203125" customWidth="1" min="1" max="1"/>
+    <col width="34.08203125" customWidth="1" min="2" max="2"/>
+    <col width="15.83203125" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>form_title</t>
         </is>
@@ -3435,12 +3422,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>(Demo) 3. ITAS LF-ONCHO FTS Results Form</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>(Uganda) 3. ITAS LF-ONCHO FTS Results Form</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>demo_lf_itas_9999_3_fts</t>
         </is>
